--- a/Блок14_надстройка_арматура.xlsx
+++ b/Блок14_надстройка_арматура.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="406">
   <si>
     <t xml:space="preserve">Блок 14 — надстройка (тех. этаж +18.350…+21.750) — потребность</t>
   </si>
@@ -123,19 +123,13 @@
     <t xml:space="preserve">Основание</t>
   </si>
   <si>
-    <t xml:space="preserve">Анкерная шайба АШ-3 (18)</t>
+    <t xml:space="preserve">Анкерная шайба АШ-4 (20)</t>
   </si>
   <si>
     <t xml:space="preserve">шт.</t>
   </si>
   <si>
-    <t xml:space="preserve">2Ø18 ригелей × 2 конца (узел «3»: верхние и нижние стержни)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Анкерная шайба АШ-4 (20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">балка 4-4 у ригеля В: 4 стержня</t>
+    <t xml:space="preserve">верх 8Ø20 каждой из 4 колонн (32, как на 5 этаже); балка 4-4 у ригеля В — 4 стержня</t>
   </si>
   <si>
     <t xml:space="preserve">Анкерная шайба АШ-6 (25)</t>
@@ -147,13 +141,13 @@
     <t xml:space="preserve">Анкерная шайба АШ-7 (28)</t>
   </si>
   <si>
-    <t xml:space="preserve">верх угловых Ø28 колонн Г/3, Г/4; 4Ø28 ригелей × 2 конца (узел «3»)</t>
+    <t xml:space="preserve">верх угловых Ø28 колонн Г/3, Г/4 (8); угловые 4Ø28 ригелей × 2 конца × 4 ригеля (32) — узел «3», Б-Б</t>
   </si>
   <si>
     <t xml:space="preserve">Анкерная шайба АШ-8 (32)</t>
   </si>
   <si>
-    <t xml:space="preserve">верх угловых Ø32 колонн В/3, В/4</t>
+    <t xml:space="preserve">верх угловых Ø32 колонн В/3, В/4 (АС-30 узел «3»)</t>
   </si>
   <si>
     <t xml:space="preserve">Масса анкерных шайб (справочно)</t>
@@ -303,7 +297,10 @@
     <t xml:space="preserve">В/3, В/4 (1-1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Г/3, Г/4 (2-2)</t>
+    <t xml:space="preserve">Г/3, Г/4 (2-2) + продолж. 5 эт.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-4 (принято)</t>
   </si>
   <si>
     <t xml:space="preserve">4-4</t>
@@ -636,7 +633,7 @@
     <t xml:space="preserve">—</t>
   </si>
   <si>
-    <t xml:space="preserve">АС-28 сеч.1-1; АС-22 рама В: над 18.350 колонны без выноски сечения → 1-1, как на 2–5 этажах; точки ванной сварки выше 18.350</t>
+    <t xml:space="preserve">АС-28 сеч.1-1; АС-22 рама В: от колонн яруса 21.750 (метки «=») длинные выноски к выноске «1-1 / 4Ø32 / 8Ø20»; точки ванной сварки выше 18.350 (+800, +1300)</t>
   </si>
   <si>
     <t xml:space="preserve">по проекту</t>
@@ -654,7 +651,7 @@
     <t xml:space="preserve">АС-28 сеч.1-1 поз.5</t>
   </si>
   <si>
-    <t xml:space="preserve">L = 2.55 м. По АС-31 Б-Б «Аш-… свыше Ø20» — у Ø20 шайб нет; анкеровка Ø20 у верха не показана (ТРЕБУЕТСЯ УТОЧНЕНИЕ).</t>
+    <t xml:space="preserve">L = 2.55 м; на верхнем конце Аш (АС-30 узел «3»: шайбы на концах стержней колонны; так же, как на 5 этаже).</t>
   </si>
   <si>
     <t xml:space="preserve">Вертикальные: угловые 4Ø32 (сеч.1-1) — ½ стержней, стык +1300</t>
@@ -666,7 +663,7 @@
     <t xml:space="preserve">Вертикальные: промежуточные 8Ø20 (сеч.1-1) — ½ стержней, стык +1300</t>
   </si>
   <si>
-    <t xml:space="preserve">L = 2.05 м. По АС-31 Б-Б «Аш-… свыше Ø20» — у Ø20 шайб нет; анкеровка Ø20 у верха не показана (ТРЕБУЕТСЯ УТОЧНЕНИЕ).</t>
+    <t xml:space="preserve">L = 2.05 м; на верхнем конце Аш (АС-30 узел «3»: шайбы на концах стержней колонны; так же, как на 5 этаже).</t>
   </si>
   <si>
     <t xml:space="preserve">10</t>
@@ -708,7 +705,7 @@
     <t xml:space="preserve">Вертикальные: угловые 4Ø28 (сеч.2-2) — ½ стержней, стык +800</t>
   </si>
   <si>
-    <t xml:space="preserve">АС-28 сеч.2-2; АС-23 рама Г: выноски «2-2 / 4Ø28 / 8Ø20» над 18.350</t>
+    <t xml:space="preserve">АС-28 сеч.2-2; АС-23 рама Г: выноски «2-2 / 4Ø28 / 8Ø20» над 18.350 (точек сварки на раме Г нет — стыки приняты как у В/3, В/4, см. «Проверки»)</t>
   </si>
   <si>
     <t xml:space="preserve">Вертикальные: промежуточные 8Ø20 (сеч.2-2) — ½ стержней, стык +800</t>
@@ -723,6 +720,33 @@
     <t xml:space="preserve">Вертикальные: промежуточные 8Ø20 (сеч.2-2) — ½ стержней, стык +1300</t>
   </si>
   <si>
+    <t xml:space="preserve">ось Г: Г/3, Г/4 (в Дм-4, Дм-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продолжение стержней колонны 5 этажа (угловые 4Ø28): от 18.300 до стыка +800 над 18.350 — ½ стержней</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АС-40, АС-41 (Дм-4, Дм-5): стержни колонны на 18.350 с Аш; АС-23 рама Г: колонна 2-2 продолжается выше — ОБНАРУЖЕНО ПРОТИВОРЕЧИЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОБНАРУЖЕНО ПРОТИВОРЕЧИЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В книге 1–5 этаж эти стержни обрезаны на 18.300 (L 2,75 / 2,25 м, Аш). При продолжении колонны вверх они удлиняются до стыка +800: +0.85 м; на объекте это один стержень 3,6 м, Аш на 18.350 не ставится.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продолжение стержней колонны 5 этажа (угловые 4Ø28): от 18.300 до стыка +1300 над 18.350 — ½ стержней</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В книге 1–5 этаж эти стержни обрезаны на 18.300 (L 2,75 / 2,25 м, Аш). При продолжении колонны вверх они удлиняются до стыка +1300: +1.35 м; на объекте это один стержень 3,6 м, Аш на 18.350 не ставится.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продолжение стержней колонны 5 этажа (промежуточные 8Ø20): от 18.300 до стыка +800 над 18.350 — ½ стержней</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продолжение стержней колонны 5 этажа (промежуточные 8Ø20): от 18.300 до стыка +1300 над 18.350 — ½ стержней</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ригели</t>
   </si>
   <si>
@@ -735,21 +759,21 @@
     <t xml:space="preserve">Продольные угловые 4Ø28 (сеч.4-4), концы с Аш</t>
   </si>
   <si>
-    <t xml:space="preserve">АС-22 верхний ярус: выноска «4-4 / 4Ø28 / 2Ø18 / 2Ø16»; L = 6500 + 2×250 (до наружной грани крайних колонн, АС-30 узел «3»)</t>
+    <t xml:space="preserve">АС-22 верхний ярус: выноски сечения на ригеле 21.750 нет — принято 4-4 по аналогии с рамой Г (АС-23); 4-4 и 5-5 армированы одинаково (АС-28); АС-28 сеч.4-4: 4Ø28 + 2Ø18 + 2Ø16; L = 6500 + 2×250 (до наружной грани крайних колонн, АС-30 узел «3»)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продольные средние верх/низ 2Ø18 (сеч.4-4), без Аш (АС-31 Б-Б: на внутренних стержнях Аш только свыше Ø20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АС-28 сеч.4-4 поз.6</t>
   </si>
   <si>
     <t xml:space="preserve">по геометрии чертежа</t>
   </si>
   <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Продольные средние верх/низ 2Ø18 (сеч.4-4), концы с Аш</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АС-28 сеч.4-4 поз.6</t>
-  </si>
-  <si>
     <t xml:space="preserve">7</t>
   </si>
   <si>
@@ -801,7 +825,7 @@
     <t xml:space="preserve">Р-Г</t>
   </si>
   <si>
-    <t xml:space="preserve">АС-23 верхний ярус: выноска «4-4 / 4Ø28 / 2Ø18 / 2Ø16»; L = 6500 + 2×250 (до наружной грани крайних колонн, АС-30 узел «3»)</t>
+    <t xml:space="preserve">АС-23 верхний ярус: выноска «4-4»; АС-28 сеч.4-4: 4Ø28 + 2Ø18 + 2Ø16; L = 6500 + 2×250 (до наружной грани крайних колонн, АС-30 узел «3»)</t>
   </si>
   <si>
     <t xml:space="preserve">Пролёт в свету 300…6200 мм, балки плиты в точках [4050]</t>
@@ -816,10 +840,10 @@
     <t xml:space="preserve">Продольные угловые 4Ø28 (сеч.5-5), концы с Аш</t>
   </si>
   <si>
-    <t xml:space="preserve">АС-26 верхний ярус: выноска «5-5 / 4Ø28 / 2Ø18 / 2Ø16»; L = 6500 + 2×250 (до наружной грани крайних колонн, АС-30 узел «3»)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Продольные средние верх/низ 2Ø18 (сеч.5-5), концы с Аш</t>
+    <t xml:space="preserve">АС-26 верхний ярус: выноска «5-5»; АС-28 сеч.5-5: 4Ø28 + 2Ø18 + 2Ø16; L = 6500 + 2×250 (до наружной грани крайних колонн, АС-30 узел «3»)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Продольные средние верх/низ 2Ø18 (сеч.5-5), без Аш (АС-31 Б-Б: на внутренних стержнях Аш только свыше Ø20)</t>
   </si>
   <si>
     <t xml:space="preserve">АС-28 сеч.5-5 поз.6</t>
@@ -840,7 +864,7 @@
     <t xml:space="preserve">Р-4</t>
   </si>
   <si>
-    <t xml:space="preserve">АС-27 верхний ярус: выноска «5-5 / 4Ø28 / 2Ø18 / 2Ø16»; L = 6500 + 2×250 (до наружной грани крайних колонн, АС-30 узел «3»)</t>
+    <t xml:space="preserve">АС-27 верхний ярус: выноска «5-5»; АС-28 сеч.5-5: 4Ø28 + 2Ø18 + 2Ø16; L = 6500 + 2×250 (до наружной грани крайних колонн, АС-30 узел «3»)</t>
   </si>
   <si>
     <t xml:space="preserve">Плита перекрытия</t>
@@ -960,7 +984,7 @@
     <t xml:space="preserve">АС-52 план 21.750 (выноски «1», «4-4»); АС-55 сеч.4-4; АС-57 узел «1»</t>
   </si>
   <si>
-    <t xml:space="preserve">Пролёт в свету 3085 мм; ригель В + заход в балку 1-1.</t>
+    <t xml:space="preserve">Пролёт в свету 3085 мм; ригель В + заход в балку 1-1; в точке 585 примыкает балка 4-4 над проёмом (узел «Д»).</t>
   </si>
   <si>
     <t xml:space="preserve">Y 710…910 (над проёмом), от балки 4-4 до балки 1-1</t>
@@ -1044,13 +1068,13 @@
     <t xml:space="preserve">2.55×4 → 1 пр.; 2.05×4 → 1 пр.</t>
   </si>
   <si>
-    <t xml:space="preserve">7×1 + 2.55×1 + 2.05×1 → 4 пр.; 7×1 → 12 пр.</t>
+    <t xml:space="preserve">7×1 + 2.55×1 + 2.05×1 → 4 пр.; 7×1 + 1.35×3 → 1 пр.; 7×1 + 1.35×1 + 0.85×3 → 1 пр.; 7×1 + 0.85×1 → 1 пр.; 7×1 → 9 пр.</t>
   </si>
   <si>
     <t xml:space="preserve">6.9×1 → 8 пр.</t>
   </si>
   <si>
-    <t xml:space="preserve">3.785×3 → 1 пр.; 2.55×2 + 2.05×3 → 1 пр.; 3.05×2 + 2.55×2 → 1 пр.; 2.05×5 → 2 пр.; 2.55×4 → 3 пр.; 3.785×1 + 3.05×2 → 1 пр.; 2.05×3 → 1 пр.</t>
+    <t xml:space="preserve">2.05×5 + 1.35×1 → 2 пр.; 2.55×4 + 1.35×1 → 3 пр.; 2.05×3 + 1.35×2 + 0.85×3 → 1 пр.; 3.785×3 → 1 пр.; 2.55×2 + 2.05×3 → 1 пр.; 3.785×1 + 3.05×2 + 1.35×1 → 1 пр.; 3.05×2 + 2.55×2 → 1 пр.; 0.85×5 → 1 пр.</t>
   </si>
   <si>
     <t xml:space="preserve">7×1 → 8 пр.</t>
@@ -1062,7 +1086,7 @@
     <t xml:space="preserve">0.42×27 → 2 пр.; 0.42×17 → 1 пр.</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96×3 + 1.24×2 + 1.04×3 + 0.22×1 → 1 пр.; 0.75×15 + 0.22×2 → 8 пр.; 1.04×11 + 0.22×1 → 3 пр.; 1.96×5 + 1.24×1 + 0.58×1 → 23 пр.; 1.04×7 + 0.75×5 + 0.58×1 → 1 пр.; 2.44×4 + 1.24×1 + 0.58×1 → 27 пр.; 2.06×3 + 1.96×2 + 1.24×1 + 0.22×1 → 1 пр.; 2.06×5 + 1.24×1 → 38 пр.; 0.75×3 + 0.58×16 → 1 пр.; 0.58×13 + 0.22×18 → 1 пр.; 0.22×32 → 1 пр.</t>
+    <t xml:space="preserve">1.96×3 + 1.24×2 + 1.04×3 + 0.22×1 → 1 пр.; 0.75×15 + 0.22×2 → 8 пр.; 1.04×11 + 0.22×1 → 3 пр.; 1.96×5 + 1.24×1 + 0.58×1 → 23 пр.; 0.58×17 + 0.22×8 → 1 пр.; 1.04×9 + 0.75×3 → 1 пр.; 2.44×4 + 1.24×1 + 0.58×1 → 27 пр.; 2.06×3 + 1.96×2 + 1.24×1 + 0.22×1 → 1 пр.; 2.06×5 + 1.24×1 → 38 пр.; 0.75×5 + 0.58×13 + 0.22×1 → 1 пр.; 0.22×41 → 1 пр.</t>
   </si>
   <si>
     <t xml:space="preserve">ИТОГО</t>
@@ -1086,7 +1110,7 @@
     <t xml:space="preserve">Колонны В/3, В/4</t>
   </si>
   <si>
-    <t xml:space="preserve">На раме В над +18.350 выноски сечения нет → сечение 1-1 (4Ø32 + 8Ø20), как на 2–5 этажах; на колоннах выше 18.350 — точки ванной сварки (стыки +800 / +1300).</t>
+    <t xml:space="preserve">АС-22 рама В: от колонн яруса 21.750 (метки «=») длинные выноски ведут к выноске «1-1 / 4Ø32 / 8Ø20» → сечение 1-1; на колоннах выше 18.350 — точки ванной сварки (стыки +800 / +1300).</t>
   </si>
   <si>
     <t xml:space="preserve">Колонны Г/3, Г/4</t>
@@ -1101,10 +1125,10 @@
     <t xml:space="preserve">От стыка над +18.350 (½ стержней на +800, ½ на +1300 — АС-32) до верха плиты 21.750 − 50: 2,55 и 2,05 м; на верхних концах угловых стержней — Аш (АС-30 узел «3», АС-31 Б-Б).</t>
   </si>
   <si>
-    <t xml:space="preserve">Ø20 колонн вверху</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АС-31 Б-Б: «Аш-… свыше Ø20» → на 8Ø20 шайб нет; как анкеруются Ø20 у верха, не показано — ТРЕБУЕТСЯ УТОЧНЕНИЕ (принято прямо, без отгиба).</t>
+    <t xml:space="preserve">Аш колонн и ригелей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АС-30 узел «3»: шайбы на верхних концах стержней колонны — приняты на все 12 стержней каждой колонны (так же, как на 5 этаже основной книги). АС-31 Б-Б: «Аш-…» на угловых стержнях ригеля, «Аш-… свыше Ø20» — на внутренних; Ø18 поз.6 ≤ Ø20 → без шайб (как в основной книге).</t>
   </si>
   <si>
     <t xml:space="preserve">Хомуты колонн</t>
@@ -1113,7 +1137,7 @@
     <t xml:space="preserve">Схема АС-32 дана до 18.350. Для тех. этажа (в свету 3400 − 600 = 2800) принят тот же порядок: 50 + 100×12 + 200 + 100×12 + 50 → 27 наружных Ø8 L=2440, внутренние Ø8 L=1960 ш.200 — 2 × 15 рядов. Уточнить.</t>
   </si>
   <si>
-    <t xml:space="preserve">Рамы В, Г — сеч.4-4, рамы 3, 4 — сеч.5-5: 4Ø28 + 2Ø18 + 2Ø16; ОС/Ос и штриховки на ярусе нет. Длина 6500 + 2 × 250 = 7,0 м (до наружной грани крайних колонн, Аш). Хомуты поз.12 ш.100 у опор / 150 в пролёте, 80×4 у балок плиты; шпильки поз.16, 17.</t>
+    <t xml:space="preserve">Рама Г — сеч.4-4 (выноска на ригеле), рамы 3, 4 — сеч.5-5; на ригеле рамы В выноски нет — принято 4-4 по аналогии с рамой Г (4-4 и 5-5 армированы одинаково: 4Ø28 + 2Ø18 + 2Ø16, АС-28); ОС/Ос и штриховки на ярусе нет. Длина 6500 + 2 × 250 = 7,0 м (до наружной грани крайних колонн, Аш). Хомуты поз.12 ш.100 у опор / 150 в пролёте, 80×4 у балок плиты; шпильки поз.16, 17.</t>
   </si>
   <si>
     <t xml:space="preserve">Плита +21.750</t>
@@ -1134,13 +1158,82 @@
     <t xml:space="preserve">ОБНАРУЖЕНО ПРОТИВОРЕЧИЕ: Г/3, Г/4</t>
   </si>
   <si>
-    <t xml:space="preserve">На раме Г колонны надстройки есть (сеч.2-2), но сварки выше 18.350 не показаны, а на развёртках Дм-4 / Дм-5 (АС-40, 41) у всех стержней на 18.350 — Аш. Принято: колонны надстройки как у В/3, В/4 (стык над 18.350). Если стержни 2-2 надстройки должны заанкериваться в Дм — длина выпусков не указана, уточнить у проектировщика.</t>
+    <t xml:space="preserve">На раме Г (АС-23) колонны надстройки есть (сеч.2-2), точек сварки выше 18.350 нет, а на развёртках Дм-4 / Дм-5 (АС-40, 41) у стержней колонны на 18.350 — Аш. В книге 1–5 этаж стержни Дм-4 / Дм-5 обрезаны на 18.300 с Аш. Принято: колонны надстройки как у В/3, В/4 (стык +800 / +1300 над 18.350), а недостающий участок стержней 5 этажа 18.300 → стык (0,85 / 1,35 м: Ø28 8,8 м, Ø20 17,6 м = 85,9 кг) добавлен в эту книгу отдельными строками «Продолжение стержней колонны 5 этажа». На объекте это один стержень 3,6 м; 8 Аш Ø28 и 16 Аш Ø20 на 18.350 в книге 1–5 этаж тогда не нужны. Если исполнять по АС-40/41 (обрыв с Аш), стержни надстройки должны заходить в узел 18.350 на длину анкеровки (на чертежах не дана) — масса примерно та же, ванной сварки нет. Уточнить у проектировщика.</t>
   </si>
   <si>
     <t xml:space="preserve">Свес 370</t>
   </si>
   <si>
     <t xml:space="preserve">Свес 370 за ось Г показан на плане 21.750; торцевых стержней сеч.6-6 и выпусков парапета на этом плане нет — не считались.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НЕЗАВИСИМАЯ ПРОВЕРКА (критик) — что исправлено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Г/3, Г/4: +85,9 кг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Участок стержней колонн Г/3, Г/4 от 18.300 до стыков +800 / +1300 не был учтён ни в 5 этаже, ни в надстройке. Добавлен (см. противоречие выше).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Ссылки на чертёж (0 кг)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ригель рамы В на 21.750 — выноски нет, принято 4-4 по аналогии с рамой Г. Колонны В/3, В/4 — выноска 1-1 есть (длинные выноски к подвалу), формулировка исправлена.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Аш</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Правило приведено к основной книге: +32 Аш Ø20 на верх колонн, −16 Аш Ø18 у ригелей (масса арматуры не меняется).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Балка 4-4 у шахты: +0,8 кг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Примыкание балки 4-4 над проёмом (узел «Д») — +2 хомута поз.13.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Бетон ригелей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сеч.4-4 (рамы В, Г) h = 630, сеч.5-5 (рамы 3, 4) h = 600 — бетон пересчитан.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НЕЗАВИСИМАЯ ПРОВЕРКА — спорно, оставлено как есть</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Принято по АС-32 (100×12 снизу и сверху) = 27 шт, как в основной книге. Узел «2» АС-29 даёт над перекрытием 100×10 — тогда 26 шт (−3,9 кг на 4 колонны).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Боковые Ø16 поз.7 в узле «3»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На узле загнуты вниз примерно на 100 мм, размер не дан — загиб не считался (≈ +2,5 кг, если считать).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Свес плиты за ригель Г</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Край плиты на 370 от оси Г, свес ≈ 145 мм за грань ригеля. Сечения 6-6 (торцевое армирование) на плане 21.750 нет — не считалось (≈ +25 кг, если проектировщик подтвердит).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОБНАРУЖЕНО ПРОТИВОРЕЧИЕ: масса С-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АС-30: «вес 4,22 кг», по геометрии 7Ø10 × 0,57 = 2,46 кг. Принято по геометрии, как в основной книге (по штампу было бы +70 кг на 40 сеток).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чего на чертежах нет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выпусков парапета, доп. стержней, марок 6-6 на плане 21.750; ж/б стен тех. этажа; закладных МН выше 18.350; колонн выше 21.750 (в узле «3» колонна кончается Аш).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтверждено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сечения колонн 1-1 / 2-2, длины 2,55 / 2,05 м, хомуты поз.10, 11; ригели 4-4 / 5-5, L = 7,0 м, хомуты 51 / 48 / 47 / 47; контур и проёмы плиты, сетка Ø10/200, балки 1-1 и 4-4, их хомуты и Аш; С-1 — 40 шт.</t>
   </si>
   <si>
     <t xml:space="preserve">КОНТРОЛЬНЫЕ ЦИФРЫ</t>
@@ -1838,7 +1931,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1948,7 +2041,7 @@
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">'По осям'!P9*'По осям'!Q9</f>
-        <v>88.9456</v>
+        <v>131.4848</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">'По осям'!S9*'По осям'!T9</f>
@@ -1956,11 +2049,11 @@
       </c>
       <c r="E5" s="7" t="n">
         <f aca="false">C5+D5</f>
-        <v>630.3536</v>
+        <v>672.8928</v>
       </c>
       <c r="F5" s="8" t="n">
         <f aca="false">E5*Исходные!$B$9</f>
-        <v>674.478352</v>
+        <v>719.995296</v>
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">'Раскрой 11,7м'!D5</f>
@@ -1972,7 +2065,7 @@
       </c>
       <c r="I5" s="11" t="n">
         <f aca="false">'Раскрой 11,7м'!H5</f>
-        <v>0.303418803418803</v>
+        <v>0.256410256410257</v>
       </c>
       <c r="J5" s="12" t="n">
         <f aca="false">MAX(F5,H5)</f>
@@ -2028,7 +2121,7 @@
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">'По осям'!P11*'По осям'!Q11</f>
-        <v>181.4976</v>
+        <v>224.8992</v>
       </c>
       <c r="D7" s="6" t="n">
         <f aca="false">'По осям'!S11*'По осям'!T11</f>
@@ -2036,27 +2129,27 @@
       </c>
       <c r="E7" s="7" t="n">
         <f aca="false">C7+D7</f>
-        <v>248.91804</v>
+        <v>292.31964</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">E7*Исходные!$B$9</f>
-        <v>266.3423028</v>
+        <v>312.7820148</v>
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">'Раскрой 11,7м'!D7</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" s="10" t="n">
         <f aca="false">'Раскрой 11,7м'!E7</f>
-        <v>288.522</v>
+        <v>317.3742</v>
       </c>
       <c r="I7" s="11" t="n">
         <f aca="false">'Раскрой 11,7м'!H7</f>
-        <v>0.137264957264957</v>
+        <v>0.0789432789432787</v>
       </c>
       <c r="J7" s="12" t="n">
         <f aca="false">MAX(F7,H7)</f>
-        <v>288.522</v>
+        <v>317.3742</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2232,15 +2325,15 @@
       </c>
       <c r="D12" s="6" t="n">
         <f aca="false">'По осям'!S16*'По осям'!T16</f>
-        <v>281.6982</v>
+        <v>282.5198</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">C12+D12</f>
-        <v>478.6926</v>
+        <v>479.5142</v>
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">E12*Исходные!$B$9</f>
-        <v>512.201082</v>
+        <v>513.080194</v>
       </c>
       <c r="G12" s="9" t="n">
         <f aca="false">'Раскрой 11,7м'!D12</f>
@@ -2252,11 +2345,11 @@
       </c>
       <c r="I12" s="11" t="n">
         <f aca="false">'Раскрой 11,7м'!H12</f>
-        <v>0.0135286935286935</v>
+        <v>0.0118355718355719</v>
       </c>
       <c r="J12" s="12" t="n">
         <f aca="false">MAX(F12,H12)</f>
-        <v>512.201082</v>
+        <v>513.080194</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2268,31 +2361,31 @@
       </c>
       <c r="C13" s="15" t="n">
         <f aca="false">SUM(C4:C12)</f>
-        <v>583.5968</v>
+        <v>669.5376</v>
       </c>
       <c r="D13" s="15" t="n">
         <f aca="false">SUM(D4:D12)</f>
-        <v>1983.05055</v>
+        <v>1983.87215</v>
       </c>
       <c r="E13" s="15" t="n">
         <f aca="false">SUM(E4:E12)</f>
-        <v>2566.64735</v>
+        <v>2653.40975</v>
       </c>
       <c r="F13" s="15" t="n">
         <f aca="false">SUM(F4:F12)</f>
-        <v>2746.3126645</v>
+        <v>2839.1484325</v>
       </c>
       <c r="G13" s="16" t="n">
         <f aca="false">SUM(G4:G12)</f>
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H13" s="15" t="n">
         <f aca="false">SUM(H4:H12)</f>
-        <v>3294.2052</v>
+        <v>3323.0574</v>
       </c>
       <c r="J13" s="15" t="n">
         <f aca="false">SUM(J4:J12)</f>
-        <v>3321.148782</v>
+        <v>3350.880094</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2304,27 +2397,27 @@
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">C13/1000</f>
-        <v>0.5835968</v>
+        <v>0.6695376</v>
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">D13/1000</f>
-        <v>1.98305055</v>
+        <v>1.98387215</v>
       </c>
       <c r="E14" s="17" t="n">
         <f aca="false">E13/1000</f>
-        <v>2.56664735</v>
+        <v>2.65340975</v>
       </c>
       <c r="F14" s="17" t="n">
         <f aca="false">F13/1000</f>
-        <v>2.7463126645</v>
+        <v>2.8391484325</v>
       </c>
       <c r="H14" s="17" t="n">
         <f aca="false">H13/1000</f>
-        <v>3.2942052</v>
+        <v>3.3230574</v>
       </c>
       <c r="J14" s="17" t="n">
         <f aca="false">J13/1000</f>
-        <v>3.321148782</v>
+        <v>3.350880094</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2332,7 +2425,7 @@
         <v>23</v>
       </c>
       <c r="E15" s="7" t="n">
-        <f aca="false">ROUND(E13-Ведомость!O66,1)+ROUND(E13-'По осям'!O17,1)</f>
+        <f aca="false">ROUND(E13-Ведомость!O70,1)+ROUND(E13-'По осям'!O17,1)</f>
         <v>0</v>
       </c>
       <c r="F15" s="19" t="s">
@@ -2357,11 +2450,11 @@
       </c>
       <c r="D18" s="21" t="n">
         <f aca="false">'По осям'!U22</f>
-        <v>11.38146</v>
+        <v>11.54076</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">C18+D18</f>
-        <v>16.10466</v>
+        <v>16.26396</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2393,7 +2486,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
@@ -2401,16 +2494,16 @@
         <v>33</v>
       </c>
       <c r="C22" s="23" t="n">
-        <f aca="false">'По осям'!P28</f>
-        <v>0</v>
+        <f aca="false">'По осям'!P29</f>
+        <v>32</v>
       </c>
       <c r="D22" s="23" t="n">
-        <f aca="false">'По осям'!S28</f>
-        <v>16</v>
+        <f aca="false">'По осям'!S29</f>
+        <v>4</v>
       </c>
       <c r="E22" s="24" t="n">
         <f aca="false">SUM(C22:D22)</f>
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>34</v>
@@ -2428,16 +2521,16 @@
         <v>33</v>
       </c>
       <c r="C23" s="23" t="n">
-        <f aca="false">'По осям'!P29</f>
+        <f aca="false">'По осям'!P31</f>
         <v>0</v>
       </c>
       <c r="D23" s="23" t="n">
-        <f aca="false">'По осям'!S29</f>
-        <v>4</v>
+        <f aca="false">'По осям'!S31</f>
+        <v>16</v>
       </c>
       <c r="E23" s="24" t="n">
         <f aca="false">SUM(C23:D23)</f>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>36</v>
@@ -2447,7 +2540,7 @@
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
@@ -2455,16 +2548,16 @@
         <v>33</v>
       </c>
       <c r="C24" s="23" t="n">
-        <f aca="false">'По осям'!P31</f>
-        <v>0</v>
+        <f aca="false">'По осям'!P32</f>
+        <v>8</v>
       </c>
       <c r="D24" s="23" t="n">
-        <f aca="false">'По осям'!S31</f>
-        <v>16</v>
+        <f aca="false">'По осям'!S32</f>
+        <v>32</v>
       </c>
       <c r="E24" s="24" t="n">
         <f aca="false">SUM(C24:D24)</f>
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>38</v>
@@ -2482,16 +2575,16 @@
         <v>33</v>
       </c>
       <c r="C25" s="23" t="n">
-        <f aca="false">'По осям'!P32</f>
+        <f aca="false">'По осям'!P33</f>
         <v>8</v>
       </c>
       <c r="D25" s="23" t="n">
-        <f aca="false">'По осям'!S32</f>
-        <v>32</v>
+        <f aca="false">'По осям'!S33</f>
+        <v>0</v>
       </c>
       <c r="E25" s="24" t="n">
         <f aca="false">SUM(C25:D25)</f>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>40</v>
@@ -2506,19 +2599,19 @@
         <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="23" t="n">
-        <f aca="false">'По осям'!P33</f>
-        <v>8</v>
-      </c>
-      <c r="D26" s="23" t="n">
-        <f aca="false">'По осям'!S33</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <f aca="false">C22*Исходные!$B$31+C23*Исходные!$B$33+C24*Исходные!$B$34+C25*Исходные!$B$35</f>
+        <v>34.32</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <f aca="false">D22*Исходные!$B$31+D23*Исходные!$B$33+D24*Исходные!$B$34+D25*Исходные!$B$35</f>
+        <v>49.12</v>
+      </c>
+      <c r="E26" s="7" t="n">
         <f aca="false">SUM(C26:D26)</f>
-        <v>8</v>
+        <v>83.44</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>42</v>
@@ -2528,24 +2621,24 @@
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <f aca="false">C22*Исходные!$B$30+C23*Исходные!$B$31+C24*Исходные!$B$33+C25*Исходные!$B$34+C26*Исходные!$B$35</f>
-        <v>21.52</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <f aca="false">D22*Исходные!$B$30+D23*Исходные!$B$31+D24*Исходные!$B$33+D25*Исходные!$B$34+D26*Исходные!$B$35</f>
-        <v>53.28</v>
-      </c>
-      <c r="E27" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C27" s="23" t="n">
+        <f aca="false">'По осям'!P34</f>
+        <v>8</v>
+      </c>
+      <c r="D27" s="23" t="n">
+        <f aca="false">'По осям'!S34</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="24" t="n">
         <f aca="false">SUM(C27:D27)</f>
-        <v>74.8</v>
+        <v>8</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>44</v>
@@ -2555,7 +2648,7 @@
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
         <v>45</v>
       </c>
@@ -2563,11 +2656,11 @@
         <v>33</v>
       </c>
       <c r="C28" s="23" t="n">
-        <f aca="false">'По осям'!P34</f>
+        <f aca="false">'По осям'!P35</f>
         <v>8</v>
       </c>
       <c r="D28" s="23" t="n">
-        <f aca="false">'По осям'!S34</f>
+        <f aca="false">'По осям'!S35</f>
         <v>0</v>
       </c>
       <c r="E28" s="24" t="n">
@@ -2590,19 +2683,19 @@
         <v>33</v>
       </c>
       <c r="C29" s="23" t="n">
-        <f aca="false">'По осям'!P35</f>
-        <v>8</v>
+        <f aca="false">'По осям'!P38</f>
+        <v>32</v>
       </c>
       <c r="D29" s="23" t="n">
-        <f aca="false">'По осям'!S35</f>
+        <f aca="false">'По осям'!S38</f>
         <v>0</v>
       </c>
       <c r="E29" s="24" t="n">
         <f aca="false">SUM(C29:D29)</f>
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G29" s="18"/>
       <c r="H29" s="18"/>
@@ -2611,25 +2704,25 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <f aca="false">ROUND(C13*Исходные!$B$9*Исходные!$B$37/1000,1)</f>
+        <v>5</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <f aca="false">ROUND(D13*Исходные!$B$9*Исходные!$B$37/1000,1)</f>
+        <v>14.9</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <f aca="false">SUM(C30:D30)</f>
+        <v>19.9</v>
+      </c>
+      <c r="F30" s="18" t="s">
         <v>49</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="23" t="n">
-        <f aca="false">'По осям'!P38</f>
-        <v>32</v>
-      </c>
-      <c r="D30" s="23" t="n">
-        <f aca="false">'По осям'!S38</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="24" t="n">
-        <f aca="false">SUM(C30:D30)</f>
-        <v>32</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>48</v>
       </c>
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
@@ -2644,19 +2737,19 @@
         <v>12</v>
       </c>
       <c r="C31" s="10" t="n">
-        <f aca="false">ROUND(C13*Исходные!$B$9*Исходные!$B$37/1000,1)</f>
-        <v>4.4</v>
+        <f aca="false">ROUND(C13*Исходные!$B$9*Исходные!$B$38/1000,1)</f>
+        <v>7.9</v>
       </c>
       <c r="D31" s="10" t="n">
-        <f aca="false">ROUND(D13*Исходные!$B$9*Исходные!$B$37/1000,1)</f>
-        <v>14.9</v>
+        <f aca="false">ROUND(D13*Исходные!$B$9*Исходные!$B$38/1000,1)</f>
+        <v>23.4</v>
       </c>
       <c r="E31" s="7" t="n">
         <f aca="false">SUM(C31:D31)</f>
-        <v>19.3</v>
+        <v>31.3</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G31" s="18"/>
       <c r="H31" s="18"/>
@@ -2665,25 +2758,25 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <f aca="false">ROUND(C13*Исходные!$B$9*Исходные!$B$38/1000,1)</f>
-        <v>6.9</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <f aca="false">ROUND(D13*Исходные!$B$9*Исходные!$B$38/1000,1)</f>
-        <v>23.3</v>
-      </c>
-      <c r="E32" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <f aca="false">ROUND(C13*Исходные!$B$9*Исходные!$B$39/1000,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <f aca="false">ROUND(D13*Исходные!$B$9*Исходные!$B$39/1000,0)</f>
+        <v>4</v>
+      </c>
+      <c r="E32" s="25" t="n">
         <f aca="false">SUM(C32:D32)</f>
-        <v>30.2</v>
+        <v>5</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
@@ -2692,25 +2785,22 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="10" t="n">
+        <f aca="false">ROUND(Исходные!$B$44*Исходные!$B$43/Исходные!$B$42,1)</f>
+        <v>35</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="E33" s="7" t="n">
+        <f aca="false">SUM(C33:D33)</f>
+        <v>35</v>
+      </c>
+      <c r="F33" s="18" t="s">
         <v>53</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <f aca="false">ROUND(C13*Исходные!$B$9*Исходные!$B$39/1000,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <f aca="false">ROUND(D13*Исходные!$B$9*Исходные!$B$39/1000,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E33" s="25" t="n">
-        <f aca="false">SUM(C33:D33)</f>
-        <v>5</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>51</v>
       </c>
       <c r="G33" s="18"/>
       <c r="H33" s="18"/>
@@ -2725,67 +2815,67 @@
         <v>12</v>
       </c>
       <c r="C34" s="10" t="n">
-        <f aca="false">ROUND(Исходные!$B$44*Исходные!$B$43/Исходные!$B$42,1)</f>
-        <v>35</v>
+        <f aca="false">ROUND(Исходные!$B$45*Исходные!$B$43/Исходные!$B$42,1)</f>
+        <v>14</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="7" t="n">
         <f aca="false">SUM(C34:D34)</f>
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G34" s="18"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
       <c r="J34" s="18"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="10" t="n">
-        <f aca="false">ROUND(Исходные!$B$45*Исходные!$B$43/Исходные!$B$42,1)</f>
-        <v>14</v>
-      </c>
-      <c r="D35" s="10"/>
+        <f aca="false">ROUND('По осям'!P22*Исходные!$B$51/100,1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <f aca="false">ROUND('По осям'!S22*Исходные!$B$52/100,1)</f>
+        <v>13.4</v>
+      </c>
       <c r="E35" s="7" t="n">
         <f aca="false">SUM(C35:D35)</f>
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G35" s="18"/>
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
     </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <f aca="false">ROUND('По осям'!P22*Исходные!$B$51/100,1)</f>
-        <v>2.1</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <f aca="false">ROUND('По осям'!S22*Исходные!$B$52/100,1)</f>
-        <v>13.2</v>
-      </c>
-      <c r="E36" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="C36" s="9" t="n">
+        <f aca="false">ROUNDUP(Исходные!$B$46*Исходные!$B$43/Исходные!$B$42,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="25" t="n">
         <f aca="false">SUM(C36:D36)</f>
-        <v>15.3</v>
+        <v>2</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G36" s="18"/>
       <c r="H36" s="18"/>
@@ -2800,16 +2890,16 @@
         <v>60</v>
       </c>
       <c r="C37" s="9" t="n">
-        <f aca="false">ROUNDUP(Исходные!$B$46*Исходные!$B$43/Исходные!$B$42,0)</f>
-        <v>2</v>
+        <f aca="false">ROUND(Исходные!$B$47*Исходные!$B$43/Исходные!$B$42,1)</f>
+        <v>35</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="25" t="n">
         <f aca="false">SUM(C37:D37)</f>
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G37" s="18"/>
       <c r="H37" s="18"/>
@@ -2821,19 +2911,19 @@
         <v>61</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C38" s="9" t="n">
-        <f aca="false">ROUND(Исходные!$B$47*Исходные!$B$43/Исходные!$B$42,1)</f>
-        <v>35</v>
+        <f aca="false">ROUNDUP(Исходные!$B$48*Исходные!$B$43/Исходные!$B$42,0)</f>
+        <v>3</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="25" t="n">
         <f aca="false">SUM(C38:D38)</f>
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G38" s="18"/>
       <c r="H38" s="18"/>
@@ -2842,13 +2932,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C39" s="9" t="n">
-        <f aca="false">ROUNDUP(Исходные!$B$48*Исходные!$B$43/Исходные!$B$42,0)</f>
+        <f aca="false">ROUNDUP(Исходные!$B$49*Исходные!$B$43/Исходные!$B$42,0)</f>
         <v>3</v>
       </c>
       <c r="D39" s="9"/>
@@ -2857,7 +2947,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G39" s="18"/>
       <c r="H39" s="18"/>
@@ -2866,22 +2956,22 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="9" t="n">
-        <f aca="false">ROUNDUP(Исходные!$B$49*Исходные!$B$43/Исходные!$B$42,0)</f>
-        <v>3</v>
-      </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <f aca="false">ROUND(Исходные!$B$50*Исходные!$B$43/Исходные!$B$42,1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="D40" s="10"/>
+      <c r="E40" s="7" t="n">
         <f aca="false">SUM(C40:D40)</f>
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G40" s="18"/>
       <c r="H40" s="18"/>
@@ -2890,51 +2980,27 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <f aca="false">ROUND(Исходные!$B$50*Исходные!$B$43/Исходные!$B$42,1)</f>
-        <v>2.1</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C41" s="10"/>
       <c r="D41" s="10"/>
       <c r="E41" s="7" t="n">
         <f aca="false">SUM(C41:D41)</f>
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G41" s="18"/>
       <c r="H41" s="18"/>
       <c r="I41" s="18"/>
       <c r="J41" s="18"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="7" t="n">
-        <f aca="false">SUM(C42:D42)</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
-    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="21">
     <mergeCell ref="F21:J21"/>
     <mergeCell ref="F22:J22"/>
     <mergeCell ref="F23:J23"/>
@@ -2956,7 +3022,6 @@
     <mergeCell ref="F39:J39"/>
     <mergeCell ref="F40:J40"/>
     <mergeCell ref="F41:J41"/>
-    <mergeCell ref="F42:J42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2982,7 +3047,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3007,10 +3072,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="Q2" s="27" t="n">
         <f aca="false">Исходные!$B$9</f>
@@ -3019,34 +3084,34 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
       <c r="G4" s="28"/>
       <c r="H4" s="28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I4" s="28"/>
       <c r="J4" s="28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K4" s="28"/>
       <c r="L4" s="28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M4" s="28"/>
       <c r="N4" s="28"/>
       <c r="O4" s="28"/>
       <c r="P4" s="28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q4" s="28"/>
       <c r="R4" s="28"/>
@@ -3058,101 +3123,101 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="J5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="P5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="P5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Q5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="S5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -3166,7 +3231,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -3191,7 +3256,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B8" s="29" t="n">
         <f aca="false">2*2*2.55+2*2*2.05</f>
@@ -3246,12 +3311,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B9" s="29"/>
       <c r="C9" s="29" t="n">
-        <f aca="false">2*2*2.55+2*2*2.05</f>
-        <v>18.4</v>
+        <f aca="false">2*2*2.55+2*2*2.05+2*2*0.85+2*2*1.35</f>
+        <v>27.2</v>
       </c>
       <c r="D9" s="29" t="n">
         <f aca="false">4*7</f>
@@ -3276,7 +3341,7 @@
       <c r="L9" s="29"/>
       <c r="M9" s="7" t="n">
         <f aca="false">SUM(B9:L9)</f>
-        <v>130.4</v>
+        <v>139.2</v>
       </c>
       <c r="N9" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(28,Исходные!$A$13:$A$25,0))</f>
@@ -3284,11 +3349,11 @@
       </c>
       <c r="O9" s="7" t="n">
         <f aca="false">M9*N9*$Q$2</f>
-        <v>674.478352</v>
+        <v>719.995296</v>
       </c>
       <c r="P9" s="31" t="n">
         <f aca="false">SUM(B9,C9)</f>
-        <v>18.4</v>
+        <v>27.2</v>
       </c>
       <c r="Q9" s="32" t="n">
         <f aca="false">N9</f>
@@ -3296,7 +3361,7 @@
       </c>
       <c r="R9" s="33" t="n">
         <f aca="false">P9*Q9*$Q$2</f>
-        <v>95.171792</v>
+        <v>140.688736</v>
       </c>
       <c r="S9" s="31" t="n">
         <f aca="false">SUM(D9,E9,F9,G9,H9,I9,J9,K9,L9)</f>
@@ -3313,7 +3378,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="29"/>
@@ -3368,15 +3433,15 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B11" s="29" t="n">
         <f aca="false">2*4*2.55+2*4*2.05</f>
         <v>36.8</v>
       </c>
       <c r="C11" s="29" t="n">
-        <f aca="false">2*4*2.55+2*4*2.05</f>
-        <v>36.8</v>
+        <f aca="false">2*4*2.55+2*4*2.05+2*4*0.85+2*4*1.35</f>
+        <v>54.4</v>
       </c>
       <c r="D11" s="29"/>
       <c r="E11" s="29"/>
@@ -3392,7 +3457,7 @@
       <c r="L11" s="29"/>
       <c r="M11" s="7" t="n">
         <f aca="false">SUM(B11:L11)</f>
-        <v>100.94</v>
+        <v>118.54</v>
       </c>
       <c r="N11" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(20,Исходные!$A$13:$A$25,0))</f>
@@ -3400,11 +3465,11 @@
       </c>
       <c r="O11" s="7" t="n">
         <f aca="false">M11*N11*$Q$2</f>
-        <v>266.3423028</v>
+        <v>312.7820148</v>
       </c>
       <c r="P11" s="31" t="n">
         <f aca="false">SUM(B11,C11)</f>
-        <v>73.6</v>
+        <v>91.2</v>
       </c>
       <c r="Q11" s="32" t="n">
         <f aca="false">N11</f>
@@ -3412,7 +3477,7 @@
       </c>
       <c r="R11" s="33" t="n">
         <f aca="false">P11*Q11*$Q$2</f>
-        <v>194.202432</v>
+        <v>240.642144</v>
       </c>
       <c r="S11" s="31" t="n">
         <f aca="false">SUM(D11,E11,F11,G11,H11,I11,J11,K11,L11)</f>
@@ -3429,7 +3494,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B12" s="29"/>
       <c r="C12" s="29"/>
@@ -3493,7 +3558,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
@@ -3557,7 +3622,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B14" s="29"/>
       <c r="C14" s="29"/>
@@ -3615,7 +3680,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B15" s="29"/>
       <c r="C15" s="29"/>
@@ -3670,7 +3735,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B16" s="29" t="n">
         <f aca="false">2*27*2.44+2*30*1.96</f>
@@ -3698,8 +3763,8 @@
       </c>
       <c r="H16" s="29"/>
       <c r="I16" s="29" t="n">
-        <f aca="false">91*1.24+43*1.04</f>
-        <v>157.56</v>
+        <f aca="false">91*1.24+45*1.04</f>
+        <v>159.64</v>
       </c>
       <c r="J16" s="29"/>
       <c r="K16" s="29" t="n">
@@ -3709,7 +3774,7 @@
       <c r="L16" s="29"/>
       <c r="M16" s="7" t="n">
         <f aca="false">SUM(B16:L16)</f>
-        <v>1211.88</v>
+        <v>1213.96</v>
       </c>
       <c r="N16" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(8,Исходные!$A$13:$A$25,0))</f>
@@ -3717,7 +3782,7 @@
       </c>
       <c r="O16" s="7" t="n">
         <f aca="false">M16*N16*$Q$2</f>
-        <v>512.201082</v>
+        <v>513.080194</v>
       </c>
       <c r="P16" s="31" t="n">
         <f aca="false">SUM(B16,C16)</f>
@@ -3733,7 +3798,7 @@
       </c>
       <c r="S16" s="31" t="n">
         <f aca="false">SUM(D16,E16,F16,G16,H16,I16,J16,K16,L16)</f>
-        <v>713.16</v>
+        <v>715.24</v>
       </c>
       <c r="T16" s="32" t="n">
         <f aca="false">N16</f>
@@ -3741,12 +3806,12 @@
       </c>
       <c r="U16" s="33" t="n">
         <f aca="false">S16*T16*$Q$2</f>
-        <v>301.417074</v>
+        <v>302.296186</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B17" s="35" t="n">
         <f aca="false">SUMPRODUCT(B8:B16,$N$8:$N$16)</f>
@@ -3754,7 +3819,7 @@
       </c>
       <c r="C17" s="35" t="n">
         <f aca="false">SUMPRODUCT(C8:C16,$N$8:$N$16)</f>
-        <v>278.1916</v>
+        <v>364.1324</v>
       </c>
       <c r="D17" s="35" t="n">
         <f aca="false">SUMPRODUCT(D8:D16,$N$8:$N$16)</f>
@@ -3778,7 +3843,7 @@
       </c>
       <c r="I17" s="35" t="n">
         <f aca="false">SUMPRODUCT(I8:I16,$N$8:$N$16)</f>
-        <v>62.2362</v>
+        <v>63.0578</v>
       </c>
       <c r="J17" s="35" t="n">
         <f aca="false">SUMPRODUCT(J8:J16,$N$8:$N$16)</f>
@@ -3798,26 +3863,26 @@
       </c>
       <c r="O17" s="12" t="n">
         <f aca="false">SUMPRODUCT(M8:M16,N8:N16)</f>
-        <v>2566.64735</v>
+        <v>2653.40975</v>
       </c>
       <c r="Q17" s="36" t="s">
         <v>21</v>
       </c>
       <c r="R17" s="12" t="n">
         <f aca="false">SUMPRODUCT(P8:P16,Q8:Q16)</f>
-        <v>583.5968</v>
+        <v>669.5376</v>
       </c>
       <c r="T17" s="36" t="s">
         <v>21</v>
       </c>
       <c r="U17" s="12" t="n">
         <f aca="false">SUMPRODUCT(S8:S16,T8:T16)</f>
-        <v>1983.05055</v>
+        <v>1983.87215</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18" s="37" t="n">
         <f aca="false">B17*$Q$2</f>
@@ -3825,7 +3890,7 @@
       </c>
       <c r="C18" s="37" t="n">
         <f aca="false">C17*$Q$2</f>
-        <v>297.665012</v>
+        <v>389.621668</v>
       </c>
       <c r="D18" s="37" t="n">
         <f aca="false">D17*$Q$2</f>
@@ -3849,7 +3914,7 @@
       </c>
       <c r="I18" s="37" t="n">
         <f aca="false">I17*$Q$2</f>
-        <v>66.592734</v>
+        <v>67.471846</v>
       </c>
       <c r="J18" s="37" t="n">
         <f aca="false">J17*$Q$2</f>
@@ -3865,23 +3930,23 @@
       </c>
       <c r="O18" s="38" t="n">
         <f aca="false">SUM(O8:O16)</f>
-        <v>2746.3126645</v>
+        <v>2839.1484325</v>
       </c>
       <c r="R18" s="38" t="n">
         <f aca="false">SUM(R8:R16)</f>
-        <v>624.448576</v>
+        <v>716.405232</v>
       </c>
       <c r="U18" s="38" t="n">
         <f aca="false">SUM(U8:U16)</f>
-        <v>2121.8640885</v>
+        <v>2122.7432005</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O19" s="7" t="n">
-        <f aca="false">ROUND(O17-Ведомость!O66,1)</f>
+        <f aca="false">ROUND(O17-Ведомость!O70,1)</f>
         <v>0</v>
       </c>
       <c r="P19" s="19" t="s">
@@ -3890,12 +3955,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="39" t="n">
         <f aca="false">2*0.6*0.6*(3.4-0.12)</f>
@@ -3906,12 +3971,12 @@
         <v>2.3616</v>
       </c>
       <c r="D22" s="39" t="n">
-        <f aca="false">0.45*(0.6-0.12)*5.9</f>
-        <v>1.2744</v>
+        <f aca="false">0.45*(0.63-0.12)*5.9</f>
+        <v>1.35405</v>
       </c>
       <c r="E22" s="39" t="n">
-        <f aca="false">0.45*(0.6-0.12)*5.9</f>
-        <v>1.2744</v>
+        <f aca="false">0.45*(0.63-0.12)*5.9</f>
+        <v>1.35405</v>
       </c>
       <c r="F22" s="39" t="n">
         <f aca="false">0.45*(0.6-0.12)*5.9</f>
@@ -3934,11 +3999,11 @@
       <c r="L22" s="39"/>
       <c r="M22" s="22" t="n">
         <f aca="false">SUM(B22:L22)</f>
-        <v>16.10466</v>
+        <v>16.26396</v>
       </c>
       <c r="O22" s="22" t="n">
         <f aca="false">M22*Исходные!$B$10</f>
-        <v>16.10466</v>
+        <v>16.26396</v>
       </c>
       <c r="P22" s="40" t="n">
         <f aca="false">SUM(B22,C22)</f>
@@ -3950,38 +4015,38 @@
       </c>
       <c r="S22" s="40" t="n">
         <f aca="false">SUM(D22,E22,F22,G22,H22,I22,J22,K22,L22)</f>
-        <v>11.38146</v>
+        <v>11.54076</v>
       </c>
       <c r="U22" s="41" t="n">
         <f aca="false">S22*Исходные!$B$10</f>
-        <v>11.38146</v>
+        <v>11.54076</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O23" s="42" t="n">
         <f aca="false">IF(M22&gt;0,O17/M22,0)</f>
-        <v>159.372960993899</v>
+        <v>163.146598368417</v>
       </c>
       <c r="R23" s="42" t="n">
         <f aca="false">IF(P22&gt;0,R17/P22,0)</f>
-        <v>123.559620596206</v>
+        <v>141.755081300813</v>
       </c>
       <c r="U23" s="42" t="n">
         <f aca="false">IF(S22&gt;0,U17/S22,0)</f>
-        <v>174.235164029922</v>
+        <v>171.901343585691</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M26" s="24" t="n">
         <f aca="false">SUM(B26:L26)</f>
@@ -3998,7 +4063,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M27" s="24" t="n">
         <f aca="false">SUM(B27:L27)</f>
@@ -4015,23 +4080,11 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" s="44" t="n">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="M28" s="24" t="n">
         <f aca="false">SUM(B28:L28)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P28" s="43" t="n">
         <f aca="false">SUM(B28,C28)</f>
@@ -4039,23 +4092,29 @@
       </c>
       <c r="S28" s="43" t="n">
         <f aca="false">SUM(D28,E28,F28,G28,H28,I28,J28,K28,L28)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
+      </c>
+      <c r="B29" s="44" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="44" t="n">
+        <v>16</v>
       </c>
       <c r="H29" s="44" t="n">
         <v>4</v>
       </c>
       <c r="M29" s="24" t="n">
         <f aca="false">SUM(B29:L29)</f>
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="P29" s="43" t="n">
         <f aca="false">SUM(B29,C29)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S29" s="43" t="n">
         <f aca="false">SUM(D29,E29,F29,G29,H29,I29,J29,K29,L29)</f>
@@ -4064,7 +4123,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M30" s="24" t="n">
         <f aca="false">SUM(B30:L30)</f>
@@ -4081,7 +4140,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H31" s="44" t="n">
         <v>16</v>
@@ -4101,7 +4160,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C32" s="44" t="n">
         <v>8</v>
@@ -4133,7 +4192,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B33" s="44" t="n">
         <v>8</v>
@@ -4153,7 +4212,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B34" s="44" t="n">
         <v>8</v>
@@ -4173,7 +4232,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C35" s="44" t="n">
         <v>8</v>
@@ -4193,7 +4252,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M36" s="24" t="n">
         <f aca="false">SUM(B36:L36)</f>
@@ -4210,7 +4269,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M37" s="24" t="n">
         <f aca="false">SUM(B37:L37)</f>
@@ -4227,7 +4286,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B38" s="44" t="n">
         <v>16</v>
@@ -4282,15 +4341,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>128</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>129</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -4299,10 +4358,10 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>130</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>131</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -4311,10 +4370,10 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>132</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>133</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
@@ -4323,10 +4382,10 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>134</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>135</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -4335,7 +4394,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B8" s="46" t="n">
         <v>11.7</v>
@@ -4343,7 +4402,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="46" t="n">
         <v>1.07</v>
@@ -4351,7 +4410,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" s="46" t="n">
         <v>1</v>
@@ -4359,10 +4418,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4471,7 +4530,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4482,7 +4541,7 @@
         <v>0.19</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4493,7 +4552,7 @@
         <v>0.19</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4504,7 +4563,7 @@
         <v>0.26</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4515,7 +4574,7 @@
         <v>0.4</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4526,7 +4585,7 @@
         <v>0.6</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4537,7 +4596,7 @@
         <v>0.77</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4548,7 +4607,7 @@
         <v>1.1</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4559,18 +4618,18 @@
         <v>1.59</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B37" s="50" t="n">
         <v>7</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D37" s="18"/>
       <c r="E37" s="18"/>
@@ -4578,13 +4637,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B38" s="50" t="n">
         <v>11</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D38" s="18"/>
       <c r="E38" s="18"/>
@@ -4592,13 +4651,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B39" s="50" t="n">
         <v>2</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
@@ -4606,12 +4665,12 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="51" t="n">
         <f aca="false">18*18</f>
@@ -4620,13 +4679,13 @@
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="52" t="n">
         <v>45.35</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
@@ -4634,13 +4693,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B44" s="50" t="n">
         <v>250</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="18"/>
@@ -4648,13 +4707,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B45" s="50" t="n">
         <v>100</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="18"/>
@@ -4662,13 +4721,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B46" s="50" t="n">
         <v>13</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D46" s="18"/>
       <c r="E46" s="18"/>
@@ -4676,13 +4735,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B47" s="50" t="n">
         <v>250</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="18"/>
@@ -4690,13 +4749,13 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B48" s="50" t="n">
         <v>15</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D48" s="18"/>
       <c r="E48" s="18"/>
@@ -4704,13 +4763,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B49" s="50" t="n">
         <v>20</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D49" s="18"/>
       <c r="E49" s="18"/>
@@ -4718,13 +4777,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B50" s="50" t="n">
         <v>15</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D50" s="18"/>
       <c r="E50" s="18"/>
@@ -4732,13 +4791,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B51" s="50" t="n">
         <v>45</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D51" s="18"/>
       <c r="E51" s="18"/>
@@ -4746,13 +4805,13 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B52" s="50" t="n">
         <v>116</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D52" s="18"/>
       <c r="E52" s="18"/>
@@ -4760,15 +4819,15 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" s="18" t="s">
         <v>166</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>167</v>
       </c>
       <c r="C55" s="18"/>
       <c r="D55" s="18"/>
@@ -4777,10 +4836,10 @@
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56" s="18" t="s">
         <v>168</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>169</v>
       </c>
       <c r="C56" s="18"/>
       <c r="D56" s="18"/>
@@ -4789,10 +4848,10 @@
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="B57" s="18" t="s">
         <v>170</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>171</v>
       </c>
       <c r="C57" s="18"/>
       <c r="D57" s="18"/>
@@ -4801,10 +4860,10 @@
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" s="18" t="s">
         <v>172</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>173</v>
       </c>
       <c r="C58" s="18"/>
       <c r="D58" s="18"/>
@@ -4813,10 +4872,10 @@
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="B59" s="18" t="s">
         <v>174</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>175</v>
       </c>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
@@ -4825,10 +4884,10 @@
     </row>
     <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B60" s="18" t="s">
         <v>176</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>177</v>
       </c>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
@@ -4876,7 +4935,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -4902,103 +4961,103 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="T4" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E5" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="18" t="s">
         <v>199</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>200</v>
       </c>
       <c r="G5" s="54" t="n">
         <v>32</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J5" s="54" t="n">
         <v>2</v>
@@ -5022,19 +5081,19 @@
         <v>64.3926</v>
       </c>
       <c r="P5" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q5" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="R5" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="R5" s="18" t="s">
-        <v>205</v>
-      </c>
       <c r="S5" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T5" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5042,28 +5101,28 @@
         <v>2</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>198</v>
-      </c>
       <c r="E6" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="18" t="s">
         <v>206</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>207</v>
       </c>
       <c r="G6" s="54" t="n">
         <v>20</v>
       </c>
       <c r="H6" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J6" s="54" t="n">
         <v>2</v>
@@ -5087,48 +5146,48 @@
         <v>50.3064</v>
       </c>
       <c r="P6" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q6" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="R6" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="Q6" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="R6" s="18" t="s">
-        <v>209</v>
-      </c>
       <c r="S6" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T6" s="18" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="E7" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>199</v>
-      </c>
       <c r="F7" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G7" s="54" t="n">
         <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J7" s="54" t="n">
         <v>2</v>
@@ -5152,19 +5211,19 @@
         <v>51.7666</v>
       </c>
       <c r="P7" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q7" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="Q7" s="18" t="s">
-        <v>204</v>
-      </c>
       <c r="R7" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S7" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T7" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5172,28 +5231,28 @@
         <v>4</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>198</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G8" s="54" t="n">
         <v>20</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J8" s="54" t="n">
         <v>2</v>
@@ -5217,19 +5276,19 @@
         <v>40.4424</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q8" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R8" s="18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S8" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T8" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5237,28 +5296,28 @@
         <v>5</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>198</v>
-      </c>
       <c r="E9" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>214</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>215</v>
       </c>
       <c r="G9" s="54" t="n">
         <v>8</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="J9" s="54" t="n">
         <v>2</v>
@@ -5282,17 +5341,17 @@
         <v>52.0452</v>
       </c>
       <c r="P9" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q9" s="56" t="s">
         <v>218</v>
-      </c>
-      <c r="Q9" s="56" t="s">
-        <v>219</v>
       </c>
       <c r="R9" s="18"/>
       <c r="S9" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T9" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5300,25 +5359,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C10" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>198</v>
-      </c>
       <c r="E10" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" s="18" t="s">
         <v>220</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>221</v>
       </c>
       <c r="G10" s="54" t="n">
         <v>8</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>200</v>
@@ -5345,17 +5404,17 @@
         <v>46.452</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q10" s="56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="R10" s="18"/>
       <c r="S10" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T10" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5363,28 +5422,28 @@
         <v>7</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C11" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="E11" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="18" t="s">
         <v>225</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>226</v>
       </c>
       <c r="G11" s="54" t="n">
         <v>28</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J11" s="54" t="n">
         <v>2</v>
@@ -5408,19 +5467,19 @@
         <v>49.3068</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q11" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="R11" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="R11" s="18" t="s">
-        <v>205</v>
-      </c>
       <c r="S11" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T11" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5428,28 +5487,28 @@
         <v>8</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="D12" s="18" t="s">
-        <v>224</v>
-      </c>
       <c r="E12" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G12" s="54" t="n">
         <v>20</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J12" s="54" t="n">
         <v>2</v>
@@ -5473,19 +5532,19 @@
         <v>50.3064</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q12" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R12" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S12" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T12" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5493,28 +5552,28 @@
         <v>9</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="E13" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="F13" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G13" s="54" t="n">
         <v>28</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J13" s="54" t="n">
         <v>2</v>
@@ -5538,19 +5597,19 @@
         <v>39.6388</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q13" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R13" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S13" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T13" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5558,28 +5617,28 @@
         <v>10</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C14" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="D14" s="18" t="s">
-        <v>224</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G14" s="54" t="n">
         <v>20</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J14" s="54" t="n">
         <v>2</v>
@@ -5603,271 +5662,279 @@
         <v>40.4424</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q14" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R14" s="18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S14" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T14" s="18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C15" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="E15" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>214</v>
-      </c>
       <c r="F15" s="18" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="G15" s="54" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="J15" s="54" t="n">
         <v>2</v>
       </c>
       <c r="K15" s="54" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="L15" s="47" t="n">
-        <v>2.44</v>
+        <v>0.85</v>
       </c>
       <c r="M15" s="55" t="n">
         <f aca="false">J15*K15*L15</f>
-        <v>131.76</v>
+        <v>3.4</v>
       </c>
       <c r="N15" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G15,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>4.834</v>
       </c>
       <c r="O15" s="7" t="n">
         <f aca="false">M15*N15</f>
-        <v>52.0452</v>
+        <v>16.4356</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="Q15" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="R15" s="18"/>
+        <v>234</v>
+      </c>
+      <c r="R15" s="18" t="s">
+        <v>235</v>
+      </c>
       <c r="S15" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T15" s="18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C16" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="E16" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>220</v>
-      </c>
       <c r="F16" s="18" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="G16" s="54" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I16" s="5" t="n">
         <v>200</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="J16" s="54" t="n">
         <v>2</v>
       </c>
       <c r="K16" s="54" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="L16" s="47" t="n">
-        <v>1.96</v>
+        <v>1.35</v>
       </c>
       <c r="M16" s="55" t="n">
         <f aca="false">J16*K16*L16</f>
-        <v>117.6</v>
+        <v>5.4</v>
       </c>
       <c r="N16" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G16,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>4.834</v>
       </c>
       <c r="O16" s="7" t="n">
         <f aca="false">M16*N16</f>
-        <v>46.452</v>
+        <v>26.1036</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="Q16" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="R16" s="18"/>
+        <v>234</v>
+      </c>
+      <c r="R16" s="18" t="s">
+        <v>237</v>
+      </c>
       <c r="S16" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="T16" s="18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G17" s="54" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H17" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="J17" s="54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="54" t="n">
         <v>4</v>
       </c>
       <c r="L17" s="47" t="n">
-        <v>7</v>
+        <v>0.85</v>
       </c>
       <c r="M17" s="55" t="n">
         <f aca="false">J17*K17*L17</f>
-        <v>28</v>
+        <v>6.8</v>
       </c>
       <c r="N17" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G17,Исходные!$A$13:$A$25,0))</f>
-        <v>4.834</v>
+        <v>2.466</v>
       </c>
       <c r="O17" s="7" t="n">
         <f aca="false">M17*N17</f>
-        <v>135.352</v>
+        <v>16.7688</v>
       </c>
       <c r="P17" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q17" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R17" s="18"/>
+        <v>233</v>
+      </c>
+      <c r="Q17" s="56" t="s">
+        <v>234</v>
+      </c>
+      <c r="R17" s="18" t="s">
+        <v>235</v>
+      </c>
       <c r="S17" s="18" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="T17" s="18" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>239</v>
       </c>
       <c r="G18" s="54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H18" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="J18" s="54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L18" s="47" t="n">
-        <v>7</v>
+        <v>1.35</v>
       </c>
       <c r="M18" s="55" t="n">
         <f aca="false">J18*K18*L18</f>
-        <v>14</v>
+        <v>10.8</v>
       </c>
       <c r="N18" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G18,Исходные!$A$13:$A$25,0))</f>
-        <v>1.998</v>
+        <v>2.466</v>
       </c>
       <c r="O18" s="7" t="n">
         <f aca="false">M18*N18</f>
-        <v>27.972</v>
+        <v>26.6328</v>
       </c>
       <c r="P18" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q18" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q18" s="56" t="s">
+        <v>234</v>
+      </c>
+      <c r="R18" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="R18" s="18"/>
       <c r="S18" s="18" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="T18" s="18" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5875,62 +5942,62 @@
         <v>15</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="G19" s="54" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="J19" s="54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="54" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="L19" s="47" t="n">
-        <v>7</v>
+        <v>2.44</v>
       </c>
       <c r="M19" s="55" t="n">
         <f aca="false">J19*K19*L19</f>
-        <v>14</v>
+        <v>131.76</v>
       </c>
       <c r="N19" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G19,Исходные!$A$13:$A$25,0))</f>
-        <v>1.578</v>
+        <v>0.395</v>
       </c>
       <c r="O19" s="7" t="n">
         <f aca="false">M19*N19</f>
-        <v>22.092</v>
+        <v>52.0452</v>
       </c>
       <c r="P19" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q19" s="18" t="s">
-        <v>237</v>
+        <v>217</v>
+      </c>
+      <c r="Q19" s="56" t="s">
+        <v>218</v>
       </c>
       <c r="R19" s="18"/>
       <c r="S19" s="18" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="T19" s="18" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5938,41 +6005,41 @@
         <v>16</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>232</v>
+        <v>70</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="G20" s="54" t="n">
         <v>8</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>246</v>
+        <v>215</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="J20" s="54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="54" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="L20" s="47" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="M20" s="55" t="n">
         <f aca="false">J20*K20*L20</f>
-        <v>105.06</v>
+        <v>117.6</v>
       </c>
       <c r="N20" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G20,Исходные!$A$13:$A$25,0))</f>
@@ -5980,85 +6047,83 @@
       </c>
       <c r="O20" s="7" t="n">
         <f aca="false">M20*N20</f>
-        <v>41.4987</v>
+        <v>46.452</v>
       </c>
       <c r="P20" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q20" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="R20" s="18" t="s">
-        <v>248</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="Q20" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="R20" s="18"/>
       <c r="S20" s="18" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="T20" s="18" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G21" s="54" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="J21" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="54" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L21" s="47" t="n">
-        <v>0.75</v>
+        <v>7</v>
       </c>
       <c r="M21" s="55" t="n">
         <f aca="false">J21*K21*L21</f>
-        <v>22.5</v>
+        <v>28</v>
       </c>
       <c r="N21" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G21,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>4.834</v>
       </c>
       <c r="O21" s="7" t="n">
         <f aca="false">M21*N21</f>
-        <v>8.8875</v>
+        <v>135.352</v>
       </c>
       <c r="P21" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q21" s="18" t="s">
-        <v>204</v>
+        <v>244</v>
+      </c>
+      <c r="Q21" s="56" t="s">
+        <v>218</v>
       </c>
       <c r="R21" s="18"/>
       <c r="S21" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T21" s="18" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6066,125 +6131,125 @@
         <v>18</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>300</v>
+        <v>200</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="J22" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="54" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L22" s="47" t="n">
-        <v>0.58</v>
+        <v>7</v>
       </c>
       <c r="M22" s="55" t="n">
         <f aca="false">J22*K22*L22</f>
-        <v>11.6</v>
+        <v>14</v>
       </c>
       <c r="N22" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G22,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>1.998</v>
       </c>
       <c r="O22" s="7" t="n">
         <f aca="false">M22*N22</f>
-        <v>4.582</v>
+        <v>27.972</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q22" s="56" t="s">
-        <v>219</v>
+        <v>247</v>
+      </c>
+      <c r="Q22" s="18" t="s">
+        <v>248</v>
       </c>
       <c r="R22" s="18"/>
       <c r="S22" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T22" s="18" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H23" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J23" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L23" s="47" t="n">
         <v>7</v>
       </c>
       <c r="M23" s="55" t="n">
         <f aca="false">J23*K23*L23</f>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="N23" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G23,Исходные!$A$13:$A$25,0))</f>
-        <v>4.834</v>
+        <v>1.578</v>
       </c>
       <c r="O23" s="7" t="n">
         <f aca="false">M23*N23</f>
-        <v>135.352</v>
+        <v>22.092</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="Q23" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R23" s="18"/>
       <c r="S23" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T23" s="18" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6192,62 +6257,64 @@
         <v>20</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="G24" s="54" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="J24" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="54" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="L24" s="47" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="M24" s="55" t="n">
         <f aca="false">J24*K24*L24</f>
-        <v>14</v>
+        <v>105.06</v>
       </c>
       <c r="N24" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G24,Исходные!$A$13:$A$25,0))</f>
-        <v>1.998</v>
+        <v>0.395</v>
       </c>
       <c r="O24" s="7" t="n">
         <f aca="false">M24*N24</f>
-        <v>27.972</v>
+        <v>41.4987</v>
       </c>
       <c r="P24" s="18" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="Q24" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R24" s="18"/>
+        <v>203</v>
+      </c>
+      <c r="R24" s="18" t="s">
+        <v>256</v>
+      </c>
       <c r="S24" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T24" s="18" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6255,62 +6322,62 @@
         <v>21</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="D25" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="F25" s="18" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="J25" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="54" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="L25" s="47" t="n">
-        <v>7</v>
+        <v>0.75</v>
       </c>
       <c r="M25" s="55" t="n">
         <f aca="false">J25*K25*L25</f>
-        <v>14</v>
+        <v>22.5</v>
       </c>
       <c r="N25" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G25,Исходные!$A$13:$A$25,0))</f>
-        <v>1.578</v>
+        <v>0.395</v>
       </c>
       <c r="O25" s="7" t="n">
         <f aca="false">M25*N25</f>
-        <v>22.092</v>
+        <v>8.8875</v>
       </c>
       <c r="P25" s="18" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="Q25" s="18" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="R25" s="18"/>
       <c r="S25" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T25" s="18" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6318,41 +6385,41 @@
         <v>22</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="G26" s="54" t="n">
         <v>8</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>246</v>
+        <v>215</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>300</v>
       </c>
       <c r="J26" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="54" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="L26" s="47" t="n">
-        <v>2.06</v>
+        <v>0.58</v>
       </c>
       <c r="M26" s="55" t="n">
         <f aca="false">J26*K26*L26</f>
-        <v>98.88</v>
+        <v>11.6</v>
       </c>
       <c r="N26" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G26,Исходные!$A$13:$A$25,0))</f>
@@ -6360,85 +6427,83 @@
       </c>
       <c r="O26" s="7" t="n">
         <f aca="false">M26*N26</f>
-        <v>39.0576</v>
+        <v>4.582</v>
       </c>
       <c r="P26" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q26" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="R26" s="18" t="s">
-        <v>259</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="Q26" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="R26" s="18"/>
       <c r="S26" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T26" s="18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G27" s="54" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="J27" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="54" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L27" s="47" t="n">
-        <v>0.75</v>
+        <v>7</v>
       </c>
       <c r="M27" s="55" t="n">
         <f aca="false">J27*K27*L27</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N27" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G27,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>4.834</v>
       </c>
       <c r="O27" s="7" t="n">
         <f aca="false">M27*N27</f>
-        <v>9.48</v>
+        <v>135.352</v>
       </c>
       <c r="P27" s="18" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="Q27" s="18" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="R27" s="18"/>
       <c r="S27" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T27" s="18" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6446,125 +6511,125 @@
         <v>24</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>300</v>
+        <v>200</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="J28" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="54" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L28" s="47" t="n">
-        <v>0.58</v>
+        <v>7</v>
       </c>
       <c r="M28" s="55" t="n">
         <f aca="false">J28*K28*L28</f>
-        <v>11.6</v>
+        <v>14</v>
       </c>
       <c r="N28" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G28,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>1.998</v>
       </c>
       <c r="O28" s="7" t="n">
         <f aca="false">M28*N28</f>
-        <v>4.582</v>
+        <v>27.972</v>
       </c>
       <c r="P28" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q28" s="56" t="s">
-        <v>219</v>
+        <v>247</v>
+      </c>
+      <c r="Q28" s="18" t="s">
+        <v>248</v>
       </c>
       <c r="R28" s="18"/>
       <c r="S28" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T28" s="18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H29" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J29" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K29" s="54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L29" s="47" t="n">
         <v>7</v>
       </c>
       <c r="M29" s="55" t="n">
         <f aca="false">J29*K29*L29</f>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="N29" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G29,Исходные!$A$13:$A$25,0))</f>
-        <v>4.834</v>
+        <v>1.578</v>
       </c>
       <c r="O29" s="7" t="n">
         <f aca="false">M29*N29</f>
-        <v>135.352</v>
+        <v>22.092</v>
       </c>
       <c r="P29" s="18" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="Q29" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R29" s="18"/>
       <c r="S29" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T29" s="18" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6572,62 +6637,64 @@
         <v>26</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="J30" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="54" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="L30" s="47" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="M30" s="55" t="n">
         <f aca="false">J30*K30*L30</f>
-        <v>14</v>
+        <v>98.88</v>
       </c>
       <c r="N30" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G30,Исходные!$A$13:$A$25,0))</f>
-        <v>1.998</v>
+        <v>0.395</v>
       </c>
       <c r="O30" s="7" t="n">
         <f aca="false">M30*N30</f>
-        <v>27.972</v>
+        <v>39.0576</v>
       </c>
       <c r="P30" s="18" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="Q30" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R30" s="18"/>
+        <v>203</v>
+      </c>
+      <c r="R30" s="18" t="s">
+        <v>267</v>
+      </c>
       <c r="S30" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T30" s="18" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6635,62 +6702,62 @@
         <v>27</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="J31" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="54" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="L31" s="47" t="n">
-        <v>7</v>
+        <v>0.75</v>
       </c>
       <c r="M31" s="55" t="n">
         <f aca="false">J31*K31*L31</f>
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N31" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G31,Исходные!$A$13:$A$25,0))</f>
-        <v>1.578</v>
+        <v>0.395</v>
       </c>
       <c r="O31" s="7" t="n">
         <f aca="false">M31*N31</f>
-        <v>22.092</v>
+        <v>9.48</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="Q31" s="18" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="R31" s="18"/>
       <c r="S31" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T31" s="18" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6698,41 +6765,41 @@
         <v>28</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D32" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="F32" s="18" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="G32" s="54" t="n">
         <v>8</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>246</v>
+        <v>215</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>300</v>
       </c>
       <c r="J32" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="54" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="L32" s="47" t="n">
-        <v>2.06</v>
+        <v>0.58</v>
       </c>
       <c r="M32" s="55" t="n">
         <f aca="false">J32*K32*L32</f>
-        <v>96.82</v>
+        <v>11.6</v>
       </c>
       <c r="N32" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G32,Исходные!$A$13:$A$25,0))</f>
@@ -6740,85 +6807,83 @@
       </c>
       <c r="O32" s="7" t="n">
         <f aca="false">M32*N32</f>
-        <v>38.2439</v>
+        <v>4.582</v>
       </c>
       <c r="P32" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q32" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="R32" s="18" t="s">
-        <v>268</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="Q32" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="R32" s="18"/>
       <c r="S32" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T32" s="18" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="J33" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="54" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="L33" s="47" t="n">
-        <v>0.75</v>
+        <v>7</v>
       </c>
       <c r="M33" s="55" t="n">
         <f aca="false">J33*K33*L33</f>
-        <v>24.75</v>
+        <v>28</v>
       </c>
       <c r="N33" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G33,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>4.834</v>
       </c>
       <c r="O33" s="7" t="n">
         <f aca="false">M33*N33</f>
-        <v>9.77625</v>
+        <v>135.352</v>
       </c>
       <c r="P33" s="18" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="Q33" s="18" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T33" s="18" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6826,125 +6891,125 @@
         <v>30</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="G34" s="54" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>300</v>
+        <v>200</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="J34" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="54" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L34" s="47" t="n">
-        <v>0.58</v>
+        <v>7</v>
       </c>
       <c r="M34" s="55" t="n">
         <f aca="false">J34*K34*L34</f>
-        <v>11.6</v>
+        <v>14</v>
       </c>
       <c r="N34" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G34,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>1.998</v>
       </c>
       <c r="O34" s="7" t="n">
         <f aca="false">M34*N34</f>
-        <v>4.582</v>
+        <v>27.972</v>
       </c>
       <c r="P34" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q34" s="56" t="s">
-        <v>219</v>
+        <v>273</v>
+      </c>
+      <c r="Q34" s="18" t="s">
+        <v>248</v>
       </c>
       <c r="R34" s="18"/>
       <c r="S34" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T34" s="18" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C35" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="D35" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="D35" s="18" t="s">
-        <v>270</v>
-      </c>
       <c r="E35" s="5" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="G35" s="54" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H35" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J35" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L35" s="47" t="n">
         <v>7</v>
       </c>
       <c r="M35" s="55" t="n">
         <f aca="false">J35*K35*L35</f>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="N35" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G35,Исходные!$A$13:$A$25,0))</f>
-        <v>4.834</v>
+        <v>1.578</v>
       </c>
       <c r="O35" s="7" t="n">
         <f aca="false">M35*N35</f>
-        <v>135.352</v>
+        <v>22.092</v>
       </c>
       <c r="P35" s="18" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q35" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R35" s="18"/>
       <c r="S35" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T35" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6952,62 +7017,64 @@
         <v>32</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C36" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="D36" s="18" t="s">
-        <v>270</v>
-      </c>
       <c r="E36" s="5" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="G36" s="54" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="J36" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="54" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="L36" s="47" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="M36" s="55" t="n">
         <f aca="false">J36*K36*L36</f>
-        <v>14</v>
+        <v>96.82</v>
       </c>
       <c r="N36" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G36,Исходные!$A$13:$A$25,0))</f>
-        <v>1.998</v>
+        <v>0.395</v>
       </c>
       <c r="O36" s="7" t="n">
         <f aca="false">M36*N36</f>
-        <v>27.972</v>
+        <v>38.2439</v>
       </c>
       <c r="P36" s="18" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="Q36" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R36" s="18"/>
+        <v>203</v>
+      </c>
+      <c r="R36" s="18" t="s">
+        <v>276</v>
+      </c>
       <c r="S36" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T36" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7015,62 +7082,62 @@
         <v>33</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C37" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="D37" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="D37" s="18" t="s">
-        <v>270</v>
-      </c>
       <c r="E37" s="5" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G37" s="54" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="J37" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="54" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="L37" s="47" t="n">
-        <v>7</v>
+        <v>0.75</v>
       </c>
       <c r="M37" s="55" t="n">
         <f aca="false">J37*K37*L37</f>
-        <v>14</v>
+        <v>24.75</v>
       </c>
       <c r="N37" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G37,Исходные!$A$13:$A$25,0))</f>
-        <v>1.578</v>
+        <v>0.395</v>
       </c>
       <c r="O37" s="7" t="n">
         <f aca="false">M37*N37</f>
-        <v>22.092</v>
+        <v>9.77625</v>
       </c>
       <c r="P37" s="18" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="Q37" s="18" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="R37" s="18"/>
       <c r="S37" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T37" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7078,41 +7145,41 @@
         <v>34</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C38" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="D38" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="D38" s="18" t="s">
-        <v>270</v>
-      </c>
       <c r="E38" s="5" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="G38" s="54" t="n">
         <v>8</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>246</v>
+        <v>215</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>300</v>
       </c>
       <c r="J38" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="54" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="L38" s="47" t="n">
-        <v>2.06</v>
+        <v>0.58</v>
       </c>
       <c r="M38" s="55" t="n">
         <f aca="false">J38*K38*L38</f>
-        <v>96.82</v>
+        <v>11.6</v>
       </c>
       <c r="N38" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G38,Исходные!$A$13:$A$25,0))</f>
@@ -7120,85 +7187,83 @@
       </c>
       <c r="O38" s="7" t="n">
         <f aca="false">M38*N38</f>
-        <v>38.2439</v>
+        <v>4.582</v>
       </c>
       <c r="P38" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q38" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="R38" s="18" t="s">
-        <v>268</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="Q38" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="R38" s="18"/>
       <c r="S38" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T38" s="18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="n">
         <v>35</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D39" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F39" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>250</v>
-      </c>
       <c r="G39" s="54" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>251</v>
+        <v>201</v>
       </c>
       <c r="J39" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="54" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="L39" s="47" t="n">
-        <v>0.75</v>
+        <v>7</v>
       </c>
       <c r="M39" s="55" t="n">
         <f aca="false">J39*K39*L39</f>
-        <v>24.75</v>
+        <v>28</v>
       </c>
       <c r="N39" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G39,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>4.834</v>
       </c>
       <c r="O39" s="7" t="n">
         <f aca="false">M39*N39</f>
-        <v>9.77625</v>
+        <v>135.352</v>
       </c>
       <c r="P39" s="18" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="Q39" s="18" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="R39" s="18"/>
       <c r="S39" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T39" s="18" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7206,62 +7271,62 @@
         <v>36</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="G40" s="54" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>300</v>
+        <v>200</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="J40" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="54" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L40" s="47" t="n">
-        <v>0.58</v>
+        <v>7</v>
       </c>
       <c r="M40" s="55" t="n">
         <f aca="false">J40*K40*L40</f>
-        <v>11.6</v>
+        <v>14</v>
       </c>
       <c r="N40" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G40,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>1.998</v>
       </c>
       <c r="O40" s="7" t="n">
         <f aca="false">M40*N40</f>
-        <v>4.582</v>
+        <v>27.972</v>
       </c>
       <c r="P40" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q40" s="56" t="s">
-        <v>219</v>
+        <v>273</v>
+      </c>
+      <c r="Q40" s="18" t="s">
+        <v>248</v>
       </c>
       <c r="R40" s="18"/>
       <c r="S40" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T40" s="18" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7269,55 +7334,55 @@
         <v>37</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D41" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F41" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>276</v>
-      </c>
       <c r="G41" s="54" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H41" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I41" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>200</v>
       </c>
       <c r="J41" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="54" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L41" s="47" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M41" s="55" t="n">
         <f aca="false">J41*K41*L41</f>
-        <v>144.9</v>
+        <v>14</v>
       </c>
       <c r="N41" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G41,Исходные!$A$13:$A$25,0))</f>
-        <v>0.617</v>
+        <v>1.578</v>
       </c>
       <c r="O41" s="7" t="n">
         <f aca="false">M41*N41</f>
-        <v>89.4033</v>
+        <v>22.092</v>
       </c>
       <c r="P41" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Q41" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="18" t="s">
@@ -7332,57 +7397,59 @@
         <v>38</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="G42" s="54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>200</v>
+        <v>215</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="J42" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="54" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="L42" s="47" t="n">
-        <v>5.575</v>
+        <v>2.06</v>
       </c>
       <c r="M42" s="55" t="n">
         <f aca="false">J42*K42*L42</f>
-        <v>72.475</v>
+        <v>96.82</v>
       </c>
       <c r="N42" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G42,Исходные!$A$13:$A$25,0))</f>
-        <v>0.617</v>
+        <v>0.395</v>
       </c>
       <c r="O42" s="7" t="n">
         <f aca="false">M42*N42</f>
-        <v>44.717075</v>
+        <v>38.2439</v>
       </c>
       <c r="P42" s="18" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="Q42" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R42" s="18"/>
+        <v>203</v>
+      </c>
+      <c r="R42" s="18" t="s">
+        <v>276</v>
+      </c>
       <c r="S42" s="18" t="s">
         <v>4</v>
       </c>
@@ -7395,55 +7462,55 @@
         <v>39</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="G43" s="54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>200</v>
+        <v>215</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>259</v>
       </c>
       <c r="J43" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="54" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="L43" s="47" t="n">
-        <v>2.775</v>
+        <v>0.75</v>
       </c>
       <c r="M43" s="55" t="n">
         <f aca="false">J43*K43*L43</f>
-        <v>5.55</v>
+        <v>24.75</v>
       </c>
       <c r="N43" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G43,Исходные!$A$13:$A$25,0))</f>
-        <v>0.617</v>
+        <v>0.395</v>
       </c>
       <c r="O43" s="7" t="n">
         <f aca="false">M43*N43</f>
-        <v>3.42435</v>
+        <v>9.77625</v>
       </c>
       <c r="P43" s="18" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="Q43" s="18" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="R43" s="18"/>
       <c r="S43" s="18" t="s">
@@ -7458,55 +7525,55 @@
         <v>40</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="G44" s="54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J44" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L44" s="47" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="M44" s="55" t="n">
         <f aca="false">J44*K44*L44</f>
-        <v>6</v>
+        <v>11.6</v>
       </c>
       <c r="N44" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G44,Исходные!$A$13:$A$25,0))</f>
-        <v>0.617</v>
+        <v>0.395</v>
       </c>
       <c r="O44" s="7" t="n">
         <f aca="false">M44*N44</f>
-        <v>3.702</v>
+        <v>4.582</v>
       </c>
       <c r="P44" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q44" s="18" t="s">
-        <v>237</v>
+        <v>263</v>
+      </c>
+      <c r="Q44" s="56" t="s">
+        <v>218</v>
       </c>
       <c r="R44" s="18"/>
       <c r="S44" s="18" t="s">
@@ -7521,25 +7588,25 @@
         <v>41</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G45" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>200</v>
@@ -7548,14 +7615,14 @@
         <v>1</v>
       </c>
       <c r="K45" s="54" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L45" s="47" t="n">
-        <v>7.045</v>
+        <v>6.9</v>
       </c>
       <c r="M45" s="55" t="n">
         <f aca="false">J45*K45*L45</f>
-        <v>126.81</v>
+        <v>144.9</v>
       </c>
       <c r="N45" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G45,Исходные!$A$13:$A$25,0))</f>
@@ -7563,20 +7630,20 @@
       </c>
       <c r="O45" s="7" t="n">
         <f aca="false">M45*N45</f>
-        <v>78.24177</v>
+        <v>89.4033</v>
       </c>
       <c r="P45" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q45" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R45" s="18"/>
       <c r="S45" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T45" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7584,25 +7651,25 @@
         <v>42</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F46" s="18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G46" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>200</v>
@@ -7614,11 +7681,11 @@
         <v>13</v>
       </c>
       <c r="L46" s="47" t="n">
-        <v>6.11</v>
+        <v>5.575</v>
       </c>
       <c r="M46" s="55" t="n">
         <f aca="false">J46*K46*L46</f>
-        <v>79.43</v>
+        <v>72.475</v>
       </c>
       <c r="N46" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G46,Исходные!$A$13:$A$25,0))</f>
@@ -7626,20 +7693,20 @@
       </c>
       <c r="O46" s="7" t="n">
         <f aca="false">M46*N46</f>
-        <v>49.00831</v>
+        <v>44.717075</v>
       </c>
       <c r="P46" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q46" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R46" s="18"/>
       <c r="S46" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T46" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7647,25 +7714,25 @@
         <v>43</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G47" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>200</v>
@@ -7674,14 +7741,14 @@
         <v>1</v>
       </c>
       <c r="K47" s="54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L47" s="47" t="n">
-        <v>3.51</v>
+        <v>2.775</v>
       </c>
       <c r="M47" s="55" t="n">
         <f aca="false">J47*K47*L47</f>
-        <v>14.04</v>
+        <v>5.55</v>
       </c>
       <c r="N47" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G47,Исходные!$A$13:$A$25,0))</f>
@@ -7689,20 +7756,20 @@
       </c>
       <c r="O47" s="7" t="n">
         <f aca="false">M47*N47</f>
-        <v>8.66268</v>
+        <v>3.42435</v>
       </c>
       <c r="P47" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q47" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R47" s="18"/>
       <c r="S47" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T47" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7710,25 +7777,25 @@
         <v>44</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F48" s="18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G48" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>200</v>
@@ -7737,14 +7804,14 @@
         <v>1</v>
       </c>
       <c r="K48" s="54" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L48" s="47" t="n">
         <v>0.4</v>
       </c>
       <c r="M48" s="55" t="n">
         <f aca="false">J48*K48*L48</f>
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="N48" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G48,Исходные!$A$13:$A$25,0))</f>
@@ -7752,20 +7819,20 @@
       </c>
       <c r="O48" s="7" t="n">
         <f aca="false">M48*N48</f>
-        <v>4.1956</v>
+        <v>3.702</v>
       </c>
       <c r="P48" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q48" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R48" s="18"/>
       <c r="S48" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T48" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7773,25 +7840,25 @@
         <v>45</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G49" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>200</v>
@@ -7800,14 +7867,14 @@
         <v>1</v>
       </c>
       <c r="K49" s="54" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L49" s="47" t="n">
-        <v>6.9</v>
+        <v>7.045</v>
       </c>
       <c r="M49" s="55" t="n">
         <f aca="false">J49*K49*L49</f>
-        <v>144.9</v>
+        <v>126.81</v>
       </c>
       <c r="N49" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G49,Исходные!$A$13:$A$25,0))</f>
@@ -7815,20 +7882,20 @@
       </c>
       <c r="O49" s="7" t="n">
         <f aca="false">M49*N49</f>
-        <v>89.4033</v>
+        <v>78.24177</v>
       </c>
       <c r="P49" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q49" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R49" s="18"/>
       <c r="S49" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T49" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7836,25 +7903,25 @@
         <v>46</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="F50" s="18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G50" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>200</v>
@@ -7866,11 +7933,11 @@
         <v>13</v>
       </c>
       <c r="L50" s="47" t="n">
-        <v>5.575</v>
+        <v>6.11</v>
       </c>
       <c r="M50" s="55" t="n">
         <f aca="false">J50*K50*L50</f>
-        <v>72.475</v>
+        <v>79.43</v>
       </c>
       <c r="N50" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G50,Исходные!$A$13:$A$25,0))</f>
@@ -7878,20 +7945,20 @@
       </c>
       <c r="O50" s="7" t="n">
         <f aca="false">M50*N50</f>
-        <v>44.717075</v>
+        <v>49.00831</v>
       </c>
       <c r="P50" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q50" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R50" s="18"/>
       <c r="S50" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T50" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7899,25 +7966,25 @@
         <v>47</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G51" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>200</v>
@@ -7926,14 +7993,14 @@
         <v>1</v>
       </c>
       <c r="K51" s="54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L51" s="47" t="n">
-        <v>2.775</v>
+        <v>3.51</v>
       </c>
       <c r="M51" s="55" t="n">
         <f aca="false">J51*K51*L51</f>
-        <v>5.55</v>
+        <v>14.04</v>
       </c>
       <c r="N51" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G51,Исходные!$A$13:$A$25,0))</f>
@@ -7941,20 +8008,20 @@
       </c>
       <c r="O51" s="7" t="n">
         <f aca="false">M51*N51</f>
-        <v>3.42435</v>
+        <v>8.66268</v>
       </c>
       <c r="P51" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q51" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R51" s="18"/>
       <c r="S51" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T51" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7962,25 +8029,25 @@
         <v>48</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="F52" s="18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G52" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>200</v>
@@ -7989,14 +8056,14 @@
         <v>1</v>
       </c>
       <c r="K52" s="54" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L52" s="47" t="n">
         <v>0.4</v>
       </c>
       <c r="M52" s="55" t="n">
         <f aca="false">J52*K52*L52</f>
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="N52" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G52,Исходные!$A$13:$A$25,0))</f>
@@ -8004,20 +8071,20 @@
       </c>
       <c r="O52" s="7" t="n">
         <f aca="false">M52*N52</f>
-        <v>3.702</v>
+        <v>4.1956</v>
       </c>
       <c r="P52" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q52" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R52" s="18"/>
       <c r="S52" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T52" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8025,25 +8092,25 @@
         <v>49</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="G53" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>200</v>
@@ -8052,14 +8119,14 @@
         <v>1</v>
       </c>
       <c r="K53" s="54" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L53" s="47" t="n">
-        <v>7.045</v>
+        <v>6.9</v>
       </c>
       <c r="M53" s="55" t="n">
         <f aca="false">J53*K53*L53</f>
-        <v>126.81</v>
+        <v>144.9</v>
       </c>
       <c r="N53" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G53,Исходные!$A$13:$A$25,0))</f>
@@ -8067,20 +8134,20 @@
       </c>
       <c r="O53" s="7" t="n">
         <f aca="false">M53*N53</f>
-        <v>78.24177</v>
+        <v>89.4033</v>
       </c>
       <c r="P53" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q53" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R53" s="18"/>
       <c r="S53" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T53" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8088,25 +8155,25 @@
         <v>50</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="G54" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>200</v>
@@ -8118,11 +8185,11 @@
         <v>13</v>
       </c>
       <c r="L54" s="47" t="n">
-        <v>6.11</v>
+        <v>5.575</v>
       </c>
       <c r="M54" s="55" t="n">
         <f aca="false">J54*K54*L54</f>
-        <v>79.43</v>
+        <v>72.475</v>
       </c>
       <c r="N54" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G54,Исходные!$A$13:$A$25,0))</f>
@@ -8130,20 +8197,20 @@
       </c>
       <c r="O54" s="7" t="n">
         <f aca="false">M54*N54</f>
-        <v>49.00831</v>
+        <v>44.717075</v>
       </c>
       <c r="P54" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q54" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R54" s="18"/>
       <c r="S54" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T54" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8151,25 +8218,25 @@
         <v>51</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="G55" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>200</v>
@@ -8178,14 +8245,14 @@
         <v>1</v>
       </c>
       <c r="K55" s="54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L55" s="47" t="n">
-        <v>3.51</v>
+        <v>2.775</v>
       </c>
       <c r="M55" s="55" t="n">
         <f aca="false">J55*K55*L55</f>
-        <v>14.04</v>
+        <v>5.55</v>
       </c>
       <c r="N55" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G55,Исходные!$A$13:$A$25,0))</f>
@@ -8193,20 +8260,20 @@
       </c>
       <c r="O55" s="7" t="n">
         <f aca="false">M55*N55</f>
-        <v>8.66268</v>
+        <v>3.42435</v>
       </c>
       <c r="P55" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q55" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R55" s="18"/>
       <c r="S55" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T55" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8214,25 +8281,25 @@
         <v>52</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F56" s="18" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="G56" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>200</v>
@@ -8241,14 +8308,14 @@
         <v>1</v>
       </c>
       <c r="K56" s="54" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L56" s="47" t="n">
         <v>0.4</v>
       </c>
       <c r="M56" s="55" t="n">
         <f aca="false">J56*K56*L56</f>
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="N56" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G56,Исходные!$A$13:$A$25,0))</f>
@@ -8256,20 +8323,20 @@
       </c>
       <c r="O56" s="7" t="n">
         <f aca="false">M56*N56</f>
-        <v>4.1956</v>
+        <v>3.702</v>
       </c>
       <c r="P56" s="18" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="Q56" s="18" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R56" s="18"/>
       <c r="S56" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T56" s="18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8277,41 +8344,41 @@
         <v>53</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F57" s="18" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G57" s="54" t="n">
         <v>10</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I57" s="5" t="s">
-        <v>288</v>
+        <v>200</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="J57" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="54" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="L57" s="47" t="n">
-        <v>0.42</v>
+        <v>7.045</v>
       </c>
       <c r="M57" s="55" t="n">
         <f aca="false">J57*K57*L57</f>
-        <v>29.82</v>
+        <v>126.81</v>
       </c>
       <c r="N57" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G57,Исходные!$A$13:$A$25,0))</f>
@@ -8319,20 +8386,20 @@
       </c>
       <c r="O57" s="7" t="n">
         <f aca="false">M57*N57</f>
-        <v>18.39894</v>
+        <v>78.24177</v>
       </c>
       <c r="P57" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q57" s="56" t="s">
-        <v>290</v>
+        <v>285</v>
+      </c>
+      <c r="Q57" s="18" t="s">
+        <v>248</v>
       </c>
       <c r="R57" s="18"/>
       <c r="S57" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T57" s="18" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8340,91 +8407,91 @@
         <v>54</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D58" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F58" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>293</v>
-      </c>
       <c r="G58" s="54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>294</v>
+        <v>200</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="J58" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="54" t="n">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="L58" s="47" t="n">
-        <v>0.22</v>
+        <v>6.11</v>
       </c>
       <c r="M58" s="55" t="n">
         <f aca="false">J58*K58*L58</f>
-        <v>15.62</v>
+        <v>79.43</v>
       </c>
       <c r="N58" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G58,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>0.617</v>
       </c>
       <c r="O58" s="7" t="n">
         <f aca="false">M58*N58</f>
-        <v>6.1699</v>
+        <v>49.00831</v>
       </c>
       <c r="P58" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q58" s="56" t="s">
-        <v>290</v>
+        <v>285</v>
+      </c>
+      <c r="Q58" s="18" t="s">
+        <v>248</v>
       </c>
       <c r="R58" s="18"/>
       <c r="S58" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T58" s="18" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="n">
         <v>55</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F59" s="18" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="G59" s="54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="J59" s="54" t="n">
         <v>1</v>
@@ -8433,229 +8500,221 @@
         <v>4</v>
       </c>
       <c r="L59" s="47" t="n">
-        <v>6.9</v>
+        <v>3.51</v>
       </c>
       <c r="M59" s="55" t="n">
         <f aca="false">J59*K59*L59</f>
-        <v>27.6</v>
+        <v>14.04</v>
       </c>
       <c r="N59" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G59,Исходные!$A$13:$A$25,0))</f>
-        <v>3.853</v>
+        <v>0.617</v>
       </c>
       <c r="O59" s="7" t="n">
         <f aca="false">M59*N59</f>
-        <v>106.3428</v>
+        <v>8.66268</v>
       </c>
       <c r="P59" s="18" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="Q59" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R59" s="18" t="s">
-        <v>302</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="R59" s="18"/>
       <c r="S59" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T59" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="n">
         <v>56</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="G60" s="54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>200</v>
       </c>
       <c r="J60" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="54" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L60" s="47" t="n">
-        <v>6.9</v>
+        <v>0.4</v>
       </c>
       <c r="M60" s="55" t="n">
         <f aca="false">J60*K60*L60</f>
-        <v>27.6</v>
+        <v>6.8</v>
       </c>
       <c r="N60" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G60,Исходные!$A$13:$A$25,0))</f>
-        <v>3.853</v>
+        <v>0.617</v>
       </c>
       <c r="O60" s="7" t="n">
         <f aca="false">M60*N60</f>
-        <v>106.3428</v>
+        <v>4.1956</v>
       </c>
       <c r="P60" s="18" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="Q60" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R60" s="18" t="s">
-        <v>306</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="R60" s="18"/>
       <c r="S60" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T60" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="n">
         <v>57</v>
       </c>
       <c r="B61" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="G61" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I61" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="F61" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="G61" s="54" t="n">
-        <v>20</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="J61" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="54" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="L61" s="47" t="n">
-        <v>3.785</v>
+        <v>0.42</v>
       </c>
       <c r="M61" s="55" t="n">
         <f aca="false">J61*K61*L61</f>
-        <v>15.14</v>
+        <v>29.82</v>
       </c>
       <c r="N61" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G61,Исходные!$A$13:$A$25,0))</f>
-        <v>2.466</v>
+        <v>0.617</v>
       </c>
       <c r="O61" s="7" t="n">
         <f aca="false">M61*N61</f>
-        <v>37.33524</v>
+        <v>18.39894</v>
       </c>
       <c r="P61" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q61" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R61" s="18" t="s">
-        <v>311</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="Q61" s="56" t="s">
+        <v>298</v>
+      </c>
+      <c r="R61" s="18"/>
       <c r="S61" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T61" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="n">
         <v>58</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>206</v>
+        <v>300</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="G62" s="54" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>202</v>
+        <v>302</v>
       </c>
       <c r="J62" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="54" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="L62" s="47" t="n">
-        <v>3.05</v>
+        <v>0.22</v>
       </c>
       <c r="M62" s="55" t="n">
         <f aca="false">J62*K62*L62</f>
-        <v>12.2</v>
+        <v>15.62</v>
       </c>
       <c r="N62" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G62,Исходные!$A$13:$A$25,0))</f>
-        <v>2.466</v>
+        <v>0.395</v>
       </c>
       <c r="O62" s="7" t="n">
         <f aca="false">M62*N62</f>
-        <v>30.0852</v>
+        <v>6.1699</v>
       </c>
       <c r="P62" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q62" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R62" s="18" t="s">
-        <v>314</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="Q62" s="56" t="s">
+        <v>298</v>
+      </c>
+      <c r="R62" s="18"/>
       <c r="S62" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T62" s="18" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8663,62 +8722,64 @@
         <v>59</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>214</v>
+        <v>307</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="G63" s="54" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="J63" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="54" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="L63" s="47" t="n">
-        <v>1.24</v>
+        <v>6.9</v>
       </c>
       <c r="M63" s="55" t="n">
         <f aca="false">J63*K63*L63</f>
-        <v>112.84</v>
+        <v>27.6</v>
       </c>
       <c r="N63" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G63,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>3.853</v>
       </c>
       <c r="O63" s="7" t="n">
         <f aca="false">M63*N63</f>
-        <v>44.5718</v>
+        <v>106.3428</v>
       </c>
       <c r="P63" s="18" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="Q63" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="R63" s="18"/>
+        <v>248</v>
+      </c>
+      <c r="R63" s="18" t="s">
+        <v>310</v>
+      </c>
       <c r="S63" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T63" s="18" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8726,138 +8787,396 @@
         <v>60</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G64" s="54" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="J64" s="54" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="54" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="L64" s="47" t="n">
-        <v>1.04</v>
+        <v>6.9</v>
       </c>
       <c r="M64" s="55" t="n">
         <f aca="false">J64*K64*L64</f>
-        <v>44.72</v>
+        <v>27.6</v>
       </c>
       <c r="N64" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G64,Исходные!$A$13:$A$25,0))</f>
-        <v>0.395</v>
+        <v>3.853</v>
       </c>
       <c r="O64" s="7" t="n">
         <f aca="false">M64*N64</f>
-        <v>17.6644</v>
+        <v>106.3428</v>
       </c>
       <c r="P64" s="18" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="Q64" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="R64" s="18"/>
+        <v>248</v>
+      </c>
+      <c r="R64" s="18" t="s">
+        <v>314</v>
+      </c>
       <c r="S64" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T64" s="18" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="n">
         <v>61</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>85</v>
+        <v>316</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F65" s="18" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="G65" s="54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H65" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I65" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="I65" s="5" t="n">
-        <v>90</v>
-      </c>
       <c r="J65" s="54" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K65" s="54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L65" s="47" t="n">
-        <v>0.57</v>
+        <v>3.785</v>
       </c>
       <c r="M65" s="55" t="n">
         <f aca="false">J65*K65*L65</f>
-        <v>159.6</v>
+        <v>15.14</v>
       </c>
       <c r="N65" s="30" t="n">
         <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G65,Исходные!$A$13:$A$25,0))</f>
-        <v>0.617</v>
+        <v>2.466</v>
       </c>
       <c r="O65" s="7" t="n">
         <f aca="false">M65*N65</f>
-        <v>98.4732</v>
+        <v>37.33524</v>
       </c>
       <c r="P65" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q65" s="56" t="s">
-        <v>219</v>
-      </c>
-      <c r="R65" s="18"/>
+        <v>318</v>
+      </c>
+      <c r="Q65" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="R65" s="18" t="s">
+        <v>319</v>
+      </c>
       <c r="S65" s="18" t="s">
         <v>4</v>
       </c>
       <c r="T65" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F66" s="20" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="G66" s="54" t="n">
+        <v>20</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="J66" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" s="54" t="n">
+        <v>4</v>
+      </c>
+      <c r="L66" s="47" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M66" s="55" t="n">
+        <f aca="false">J66*K66*L66</f>
+        <v>12.2</v>
+      </c>
+      <c r="N66" s="30" t="n">
+        <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G66,Исходные!$A$13:$A$25,0))</f>
+        <v>2.466</v>
+      </c>
+      <c r="O66" s="7" t="n">
+        <f aca="false">M66*N66</f>
+        <v>30.0852</v>
+      </c>
+      <c r="P66" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q66" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="R66" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="S66" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="T66" s="18" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="G67" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J67" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="54" t="n">
+        <v>91</v>
+      </c>
+      <c r="L67" s="47" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M67" s="55" t="n">
+        <f aca="false">J67*K67*L67</f>
+        <v>112.84</v>
+      </c>
+      <c r="N67" s="30" t="n">
+        <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G67,Исходные!$A$13:$A$25,0))</f>
+        <v>0.395</v>
+      </c>
+      <c r="O67" s="7" t="n">
+        <f aca="false">M67*N67</f>
+        <v>44.5718</v>
+      </c>
+      <c r="P67" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q67" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="R67" s="18"/>
+      <c r="S67" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="T67" s="18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="D68" s="18" t="s">
         <v>329</v>
       </c>
-      <c r="M66" s="38" t="n">
-        <f aca="false">SUM(M5:M65)</f>
-        <v>2730.25</v>
-      </c>
-      <c r="O66" s="38" t="n">
-        <f aca="false">SUM(O5:O65)</f>
-        <v>2566.64735</v>
+      <c r="E68" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="G68" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J68" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" s="54" t="n">
+        <v>45</v>
+      </c>
+      <c r="L68" s="47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M68" s="55" t="n">
+        <f aca="false">J68*K68*L68</f>
+        <v>46.8</v>
+      </c>
+      <c r="N68" s="30" t="n">
+        <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G68,Исходные!$A$13:$A$25,0))</f>
+        <v>0.395</v>
+      </c>
+      <c r="O68" s="7" t="n">
+        <f aca="false">M68*N68</f>
+        <v>18.486</v>
+      </c>
+      <c r="P68" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q68" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="R68" s="18"/>
+      <c r="S68" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="T68" s="18" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="G69" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="J69" s="54" t="n">
+        <v>40</v>
+      </c>
+      <c r="K69" s="54" t="n">
+        <v>7</v>
+      </c>
+      <c r="L69" s="47" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M69" s="55" t="n">
+        <f aca="false">J69*K69*L69</f>
+        <v>159.6</v>
+      </c>
+      <c r="N69" s="30" t="n">
+        <f aca="false">INDEX(Исходные!$B$13:$B$25,MATCH(G69,Исходные!$A$13:$A$25,0))</f>
+        <v>0.617</v>
+      </c>
+      <c r="O69" s="7" t="n">
+        <f aca="false">M69*N69</f>
+        <v>98.4732</v>
+      </c>
+      <c r="P69" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q69" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="R69" s="18"/>
+      <c r="S69" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="T69" s="18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F70" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="M70" s="38" t="n">
+        <f aca="false">SUM(M5:M69)</f>
+        <v>2758.73</v>
+      </c>
+      <c r="O70" s="38" t="n">
+        <f aca="false">SUM(O5:O69)</f>
+        <v>2653.40975</v>
       </c>
     </row>
   </sheetData>
@@ -8889,36 +9208,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8926,7 +9245,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C4" s="49" t="n">
         <v>18.4</v>
@@ -8951,7 +9270,7 @@
         <v>0.213675213675214</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8959,10 +9278,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C5" s="49" t="n">
-        <v>130.4</v>
+        <v>139.2</v>
       </c>
       <c r="D5" s="44" t="n">
         <v>16</v>
@@ -8973,18 +9292,18 @@
       </c>
       <c r="F5" s="8" t="n">
         <f aca="false">C5*INDEX(Исходные!$B$13:$B$25,MATCH(A5,Исходные!$A$13:$A$25,0))</f>
-        <v>630.3536</v>
+        <v>672.8928</v>
       </c>
       <c r="G5" s="8" t="n">
         <f aca="false">E5-F5</f>
-        <v>274.5712</v>
+        <v>232.032</v>
       </c>
       <c r="H5" s="57" t="n">
         <f aca="false">IF(E5&gt;0,G5/E5,0)</f>
-        <v>0.303418803418803</v>
+        <v>0.256410256410257</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8992,7 +9311,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C6" s="49" t="n">
         <v>55.2</v>
@@ -9017,7 +9336,7 @@
         <v>0.41025641025641</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9025,32 +9344,32 @@
         <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C7" s="49" t="n">
-        <v>100.94</v>
+        <v>118.54</v>
       </c>
       <c r="D7" s="44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="8" t="n">
         <f aca="false">D7*Исходные!$B$8*INDEX(Исходные!$B$13:$B$25,MATCH(A7,Исходные!$A$13:$A$25,0))</f>
-        <v>288.522</v>
+        <v>317.3742</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">C7*INDEX(Исходные!$B$13:$B$25,MATCH(A7,Исходные!$A$13:$A$25,0))</f>
-        <v>248.91804</v>
+        <v>292.31964</v>
       </c>
       <c r="G7" s="8" t="n">
         <f aca="false">E7-F7</f>
-        <v>39.60396</v>
+        <v>25.0545599999999</v>
       </c>
       <c r="H7" s="57" t="n">
         <f aca="false">IF(E7&gt;0,G7/E7,0)</f>
-        <v>0.137264957264957</v>
+        <v>0.0789432789432787</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9058,7 +9377,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C8" s="49" t="n">
         <v>56</v>
@@ -9083,7 +9402,7 @@
         <v>0.401709401709402</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9091,7 +9410,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C9" s="49" t="n">
         <v>56</v>
@@ -9116,7 +9435,7 @@
         <v>0.401709401709402</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9124,7 +9443,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C10" s="49" t="n">
         <v>1071.61</v>
@@ -9149,7 +9468,7 @@
         <v>0.119321170282709</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9157,7 +9476,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C11" s="49" t="n">
         <v>29.82</v>
@@ -9182,7 +9501,7 @@
         <v>0.15042735042735</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9190,10 +9509,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C12" s="49" t="n">
-        <v>1211.88</v>
+        <v>1213.96</v>
       </c>
       <c r="D12" s="44" t="n">
         <v>105</v>
@@ -9204,48 +9523,48 @@
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">C12*INDEX(Исходные!$B$13:$B$25,MATCH(A12,Исходные!$A$13:$A$25,0))</f>
-        <v>478.6926</v>
+        <v>479.5142</v>
       </c>
       <c r="G12" s="8" t="n">
         <f aca="false">E12-F12</f>
-        <v>6.56489999999997</v>
+        <v>5.74330000000003</v>
       </c>
       <c r="H12" s="57" t="n">
         <f aca="false">IF(E12&gt;0,G12/E12,0)</f>
-        <v>0.0135286935286935</v>
+        <v>0.0118355718355719</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D13" s="58" t="n">
         <f aca="false">SUM(D4:D12)</f>
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E13" s="38" t="n">
         <f aca="false">SUM(E4:E12)</f>
-        <v>3294.2052</v>
+        <v>3323.0574</v>
       </c>
       <c r="F13" s="38" t="n">
         <f aca="false">SUM(F4:F12)</f>
-        <v>2566.64735</v>
+        <v>2653.40975</v>
       </c>
       <c r="G13" s="38" t="n">
         <f aca="false">SUM(G4:G12)</f>
-        <v>727.55785</v>
+        <v>669.64765</v>
       </c>
       <c r="H13" s="59" t="n">
         <f aca="false">IF(E13&gt;0,G13/E13,0)</f>
-        <v>0.220859905752076</v>
+        <v>0.201515523024068</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -9264,7 +9583,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -9273,148 +9592,250 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="60" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="60" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="60" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="60" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="60" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="60" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="60" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="60" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="60" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="60" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="60" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="B18" s="61" t="n">
-        <f aca="false">Ведомость!O66</f>
-        <v>2566.64735</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>381</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="60" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="62" t="n">
+        <v>383</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="60" t="s">
+        <v>385</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="60" t="s">
+        <v>387</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="60" t="s">
+        <v>389</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="60" t="s">
+        <v>368</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="60" t="s">
+        <v>395</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="60" t="s">
+        <v>397</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="60" t="s">
+        <v>399</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="60" t="s">
+        <v>401</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="60" t="s">
+        <v>404</v>
+      </c>
+      <c r="B33" s="61" t="n">
+        <f aca="false">Ведомость!O70</f>
+        <v>2653.40975</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="62" t="n">
         <f aca="false">'По осям'!M22</f>
-        <v>16.10466</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="60" t="s">
-        <v>374</v>
-      </c>
-      <c r="B20" s="63" t="n">
+        <v>16.26396</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="60" t="s">
+        <v>405</v>
+      </c>
+      <c r="B35" s="63" t="n">
         <f aca="false">ABS('По осям'!O19)+ABS(потребность!E15)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
